--- a/input_processing/reg_estimates_ES_toClean/reg_retirement_ES.xlsx
+++ b/input_processing/reg_estimates_ES_toClean/reg_retirement_ES.xlsx
@@ -54,7 +54,7 @@
     <t>Notes:</t>
   </si>
   <si>
-    <t>Regions: ES1 = Noroeste , ES2 = Noreste , ES3 = Madrid , ES4 =Centro , ES5 = Este , ES5 = Sur , ES5 = Canarias.</t>
+    <t>Regions: ES1 =  Noroeste , ES2 = Noreste , ES3 = Madrid , ES4 =  Centro , ES5 = Este , ES6=  Sur , ES7 = ,  Canarias.</t>
   </si>
   <si>
     <t>Goodness of fit</t>
@@ -90,7 +90,7 @@
     <t>Reached_Retirement_Age</t>
   </si>
   <si>
-    <t>Les_c3_NotEmployed_L1</t>
+    <t>Les_c2_NotEmployed_L1</t>
   </si>
   <si>
     <t>Ydses_c5_Q2_L1</t>
@@ -153,16 +153,16 @@
     <t>Log likelihood</t>
   </si>
   <si>
-    <t>Reached_Retirement_Age_Les_c3_NotEmployed_L1</t>
+    <t>Reached_Retirement_Age_Les_c2_NotEmployed_L1</t>
   </si>
   <si>
-    <t>Reached_Retirement_Age_Sp</t>
+    <t>Reached_Retirement_Age_Sp_L1</t>
   </si>
   <si>
-    <t>Elig_pen_Sp</t>
+    <t>Elig_pen_Sp_L1</t>
   </si>
   <si>
-    <t>Elig_pen_L1_Sp</t>
+    <t>Elig_pen_L1_Sp_L1</t>
   </si>
   <si>
     <t>Lessp_c3_NotEmployed_L1</t>
@@ -484,13 +484,13 @@
         <v>41</v>
       </c>
       <c r="B5">
-        <v>0.32015012213424909</v>
+        <v>0.32016434260509796</v>
       </c>
       <c r="E5" t="s">
         <v>43</v>
       </c>
       <c r="F5">
-        <v>1686.3999754828105</v>
+        <v>1686.3826534733244</v>
       </c>
     </row>
     <row r="6">
@@ -498,13 +498,13 @@
         <v>42</v>
       </c>
       <c r="B6">
-        <v>21275</v>
+        <v>21276</v>
       </c>
       <c r="E6" t="s">
         <v>44</v>
       </c>
       <c r="F6">
-        <v>-4802772.8732007602</v>
+        <v>-4802802.9741875418</v>
       </c>
     </row>
     <row r="9">
@@ -517,13 +517,13 @@
         <v>41</v>
       </c>
       <c r="B11">
-        <v>0.32463500320489191</v>
+        <v>0.32501950235748978</v>
       </c>
       <c r="E11" t="s">
         <v>43</v>
       </c>
       <c r="F11">
-        <v>3430.1690579460264</v>
+        <v>3443.7101888757511</v>
       </c>
     </row>
     <row r="12">
@@ -537,7 +537,7 @@
         <v>44</v>
       </c>
       <c r="F12">
-        <v>-10768081.384756271</v>
+        <v>-10761951.526744192</v>
       </c>
     </row>
   </sheetData>
@@ -634,76 +634,76 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>0.28886228311706291</v>
+        <v>0.2887942671573514</v>
       </c>
       <c r="C2">
-        <v>0.0032774275453376781</v>
+        <v>0.0032772000983176466</v>
       </c>
       <c r="D2">
-        <v>0.0004241711089230714</v>
+        <v>0.00042483191885534346</v>
       </c>
       <c r="E2">
-        <v>-2.5273815145836423e-06</v>
+        <v>-2.5317882363579936e-06</v>
       </c>
       <c r="F2">
-        <v>0.00012276989436466675</v>
+        <v>0.00012284936470375972</v>
       </c>
       <c r="G2">
-        <v>0.00061150522078228355</v>
+        <v>0.00061169123473884548</v>
       </c>
       <c r="H2">
-        <v>0.00031958539627207933</v>
+        <v>0.00031967730147480588</v>
       </c>
       <c r="I2">
-        <v>9.2277019913184584e-05</v>
+        <v>9.202019046648082e-05</v>
       </c>
       <c r="J2">
-        <v>-7.2875167281320871e-05</v>
+        <v>-7.331760072023586e-05</v>
       </c>
       <c r="K2">
-        <v>0.00011367285074757817</v>
+        <v>0.00011337716315218516</v>
       </c>
       <c r="L2">
-        <v>-0.00019337528582403249</v>
+        <v>-0.00019397742251601774</v>
       </c>
       <c r="M2">
-        <v>-5.7941091450655506e-05</v>
+        <v>-5.7890159434744083e-05</v>
       </c>
       <c r="N2">
-        <v>-0.00044511384326082338</v>
+        <v>-0.00044495405509703144</v>
       </c>
       <c r="O2">
-        <v>-0.00074793070381997924</v>
+        <v>-0.00074780033940842635</v>
       </c>
       <c r="P2">
-        <v>-0.0015540246346103083</v>
+        <v>-0.001553361962015571</v>
       </c>
       <c r="Q2">
-        <v>0.00037473684200277379</v>
+        <v>0.00037471880904776087</v>
       </c>
       <c r="R2">
-        <v>0.00044966432280574709</v>
+        <v>0.00044969172702185364</v>
       </c>
       <c r="S2">
-        <v>0.00083209192765267438</v>
+        <v>0.0008309067437706273</v>
       </c>
       <c r="T2">
-        <v>0.00051636486182710995</v>
+        <v>0.00051643597614740725</v>
       </c>
       <c r="U2">
-        <v>0.00017084223439435857</v>
+        <v>0.00017082526894713008</v>
       </c>
       <c r="V2">
-        <v>0.00073688752101665222</v>
+        <v>0.00073700127852097672</v>
       </c>
       <c r="W2">
-        <v>-7.9075494791071407e-05</v>
+        <v>-7.9151029552920537e-05</v>
       </c>
       <c r="X2">
-        <v>0.00017967249437391601</v>
+        <v>0.00018073783339145636</v>
       </c>
       <c r="Y2">
-        <v>-0.016786004743844087</v>
+        <v>-0.016808861133236104</v>
       </c>
     </row>
     <row r="3">
@@ -711,76 +711,76 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>-0.19449677421958298</v>
+        <v>-0.19443227834433768</v>
       </c>
       <c r="C3">
-        <v>0.0004241711089230714</v>
+        <v>0.00042483191885534346</v>
       </c>
       <c r="D3">
-        <v>0.0083819818405408142</v>
+        <v>0.0083841316967444013</v>
       </c>
       <c r="E3">
-        <v>-6.7406988300632627e-05</v>
+        <v>-6.7423446384728058e-05</v>
       </c>
       <c r="F3">
-        <v>-0.0062665409153839086</v>
+        <v>-0.0062672334140308275</v>
       </c>
       <c r="G3">
-        <v>-0.0057445743684857702</v>
+        <v>-0.0057452281984461551</v>
       </c>
       <c r="H3">
-        <v>0.00032547362057806784</v>
+        <v>0.00032557029444143723</v>
       </c>
       <c r="I3">
-        <v>0.00071316978225839092</v>
+        <v>0.00071360480317597588</v>
       </c>
       <c r="J3">
-        <v>0.0058492891862881313</v>
+        <v>0.0058494260028782857</v>
       </c>
       <c r="K3">
-        <v>-0.00011695211600249583</v>
+        <v>-0.00011665190321906438</v>
       </c>
       <c r="L3">
-        <v>0.00050319387980053698</v>
+        <v>0.00050380571806615815</v>
       </c>
       <c r="M3">
-        <v>0.00029895339810032118</v>
+        <v>0.00029900318018807794</v>
       </c>
       <c r="N3">
-        <v>0.00037288580278485584</v>
+        <v>0.00037284900316576081</v>
       </c>
       <c r="O3">
-        <v>0.00060563612340472361</v>
+        <v>0.00060577660682216081</v>
       </c>
       <c r="P3">
-        <v>-0.00050893754970762761</v>
+        <v>-0.00050972634126932037</v>
       </c>
       <c r="Q3">
-        <v>0.00081544929062930816</v>
+        <v>0.0008158134524309385</v>
       </c>
       <c r="R3">
-        <v>0.0014438308230710073</v>
+        <v>0.0014442747913062243</v>
       </c>
       <c r="S3">
-        <v>0.0014061250129435076</v>
+        <v>0.001407541414986945</v>
       </c>
       <c r="T3">
-        <v>0.0012629612017679426</v>
+        <v>0.001263294423463554</v>
       </c>
       <c r="U3">
-        <v>0.0015359531350203626</v>
+        <v>0.0015363959200552016</v>
       </c>
       <c r="V3">
-        <v>0.001311178040704606</v>
+        <v>0.0013115773147099365</v>
       </c>
       <c r="W3">
-        <v>-6.0076720498855943e-05</v>
+        <v>-6.0050833899493589e-05</v>
       </c>
       <c r="X3">
-        <v>0.00020807677731464469</v>
+        <v>0.00020734956898646462</v>
       </c>
       <c r="Y3">
-        <v>-0.2606092566568865</v>
+        <v>-0.26068014295401309</v>
       </c>
     </row>
     <row r="4">
@@ -788,76 +788,76 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>0.0029490041894145156</v>
+        <v>0.0029485875606328096</v>
       </c>
       <c r="C4">
-        <v>-2.5273815145836423e-06</v>
+        <v>-2.5317882363579936e-06</v>
       </c>
       <c r="D4">
-        <v>-6.7406988300632627e-05</v>
+        <v>-6.7423446384728058e-05</v>
       </c>
       <c r="E4">
-        <v>5.4612082400913683e-07</v>
+        <v>5.4624661410713258e-07</v>
       </c>
       <c r="F4">
-        <v>5.3963462650899116e-05</v>
+        <v>5.3968788625929638e-05</v>
       </c>
       <c r="G4">
-        <v>4.9415472377848751e-05</v>
+        <v>4.9420569782659637e-05</v>
       </c>
       <c r="H4">
-        <v>-2.2156233001565425e-06</v>
+        <v>-2.2163410276575095e-06</v>
       </c>
       <c r="I4">
-        <v>-5.4258089138335806e-06</v>
+        <v>-5.4288528804621259e-06</v>
       </c>
       <c r="J4">
-        <v>-5.3022978022562901e-05</v>
+        <v>-5.3024057438836605e-05</v>
       </c>
       <c r="K4">
-        <v>1.1189365428499978e-06</v>
+        <v>1.1169784064416069e-06</v>
       </c>
       <c r="L4">
-        <v>-4.1832564008674944e-06</v>
+        <v>-4.1874440949755346e-06</v>
       </c>
       <c r="M4">
-        <v>-2.2549450359362003e-06</v>
+        <v>-2.2553300544623354e-06</v>
       </c>
       <c r="N4">
-        <v>-2.578212703962233e-06</v>
+        <v>-2.5780367690972491e-06</v>
       </c>
       <c r="O4">
-        <v>-3.8693355835524149e-06</v>
+        <v>-3.8704749348174414e-06</v>
       </c>
       <c r="P4">
-        <v>4.2255046483836902e-06</v>
+        <v>4.2309286353634087e-06</v>
       </c>
       <c r="Q4">
-        <v>-6.0028054226119202e-06</v>
+        <v>-6.0054923637039605e-06</v>
       </c>
       <c r="R4">
-        <v>-1.0773862347420956e-05</v>
+        <v>-1.077712555550578e-05</v>
       </c>
       <c r="S4">
-        <v>-1.0675723241624991e-05</v>
+        <v>-1.0685400757698298e-05</v>
       </c>
       <c r="T4">
-        <v>-9.5137999705481938e-06</v>
+        <v>-9.5162780795942856e-06</v>
       </c>
       <c r="U4">
-        <v>-1.1756102432024641e-05</v>
+        <v>-1.1759368423350442e-05</v>
       </c>
       <c r="V4">
-        <v>-9.5504226583854651e-06</v>
+        <v>-9.5534058688779026e-06</v>
       </c>
       <c r="W4">
-        <v>3.8261469408698318e-07</v>
+        <v>3.8245581064729384e-07</v>
       </c>
       <c r="X4">
-        <v>-1.0672267744552206e-06</v>
+        <v>-1.0624288981172418e-06</v>
       </c>
       <c r="Y4">
-        <v>0.0020807988194184255</v>
+        <v>0.0020813413306304922</v>
       </c>
     </row>
     <row r="5">
@@ -865,76 +865,76 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>1.567215284086199</v>
+        <v>1.567226700422804</v>
       </c>
       <c r="C5">
-        <v>0.00012276989436466675</v>
+        <v>0.00012284936470375972</v>
       </c>
       <c r="D5">
-        <v>-0.0062665409153839086</v>
+        <v>-0.0062672334140308275</v>
       </c>
       <c r="E5">
-        <v>5.3963462650899116e-05</v>
+        <v>5.3968788625929638e-05</v>
       </c>
       <c r="F5">
-        <v>0.014396478317066745</v>
+        <v>0.014396716369991434</v>
       </c>
       <c r="G5">
-        <v>0.0086965691269616733</v>
+        <v>0.0086969395515247797</v>
       </c>
       <c r="H5">
-        <v>8.9683230638598621e-05</v>
+        <v>8.9646471711207071e-05</v>
       </c>
       <c r="I5">
-        <v>-0.00012653729951742228</v>
+        <v>-0.0001265523761466718</v>
       </c>
       <c r="J5">
-        <v>-0.011854942445491623</v>
+        <v>-0.011855212437201654</v>
       </c>
       <c r="K5">
-        <v>0.0017889662486112743</v>
+        <v>0.0017891674068608154</v>
       </c>
       <c r="L5">
-        <v>-0.00026379697373673378</v>
+        <v>-0.00026378356889011217</v>
       </c>
       <c r="M5">
-        <v>0.00018873691483347818</v>
+        <v>0.00018874269157246291</v>
       </c>
       <c r="N5">
-        <v>0.00063675129607465575</v>
+        <v>0.0006368582083605169</v>
       </c>
       <c r="O5">
-        <v>0.0013453403113298928</v>
+        <v>0.0013453521981434576</v>
       </c>
       <c r="P5">
-        <v>9.1703187757349869e-05</v>
+        <v>9.1680635442258074e-05</v>
       </c>
       <c r="Q5">
-        <v>-0.00027253493038349036</v>
+        <v>-0.00027265044014394141</v>
       </c>
       <c r="R5">
-        <v>-0.00038707854340498671</v>
+        <v>-0.00038716513852304207</v>
       </c>
       <c r="S5">
-        <v>-0.00061029048194654071</v>
+        <v>-0.00061038663719111853</v>
       </c>
       <c r="T5">
-        <v>-0.00055778335818701397</v>
+        <v>-0.00055785807744340721</v>
       </c>
       <c r="U5">
-        <v>-0.00045355422815356386</v>
+        <v>-0.00045367507191610562</v>
       </c>
       <c r="V5">
-        <v>-0.00030286210280648825</v>
+        <v>-0.00030297118443714348</v>
       </c>
       <c r="W5">
-        <v>-6.8679618888095595e-05</v>
+        <v>-6.8673621271978305e-05</v>
       </c>
       <c r="X5">
-        <v>0.00058318881328912886</v>
+        <v>0.00058315810217423464</v>
       </c>
       <c r="Y5">
-        <v>0.18104754929897471</v>
+        <v>0.18106981320598359</v>
       </c>
     </row>
     <row r="6">
@@ -942,76 +942,76 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>1.3400184234619177</v>
+        <v>1.3400300852774567</v>
       </c>
       <c r="C6">
-        <v>0.00061150522078228355</v>
+        <v>0.00061169123473884548</v>
       </c>
       <c r="D6">
-        <v>-0.0057445743684857702</v>
+        <v>-0.0057452281984461551</v>
       </c>
       <c r="E6">
-        <v>4.9415472377848751e-05</v>
+        <v>4.9420569782659637e-05</v>
       </c>
       <c r="F6">
-        <v>0.0086965691269616733</v>
+        <v>0.0086969395515247797</v>
       </c>
       <c r="G6">
-        <v>0.016882581663273818</v>
+        <v>0.016883113258583576</v>
       </c>
       <c r="H6">
-        <v>0.00022540557178631418</v>
+        <v>0.00022543583567750936</v>
       </c>
       <c r="I6">
-        <v>0.00043624020772464224</v>
+        <v>0.00043622779977941454</v>
       </c>
       <c r="J6">
-        <v>-0.010471634473984352</v>
+        <v>-0.010471894121715189</v>
       </c>
       <c r="K6">
-        <v>0.00019015271266200305</v>
+        <v>0.00019013702091490343</v>
       </c>
       <c r="L6">
-        <v>-0.00019007480181538333</v>
+        <v>-0.00019010366840431503</v>
       </c>
       <c r="M6">
-        <v>0.00022282598577271374</v>
+        <v>0.0002227411949269377</v>
       </c>
       <c r="N6">
-        <v>-8.4400786173235987e-05</v>
+        <v>-8.4553526749065605e-05</v>
       </c>
       <c r="O6">
-        <v>0.00026693663249364487</v>
+        <v>0.00026676730403549578</v>
       </c>
       <c r="P6">
-        <v>0.00017720029612834642</v>
+        <v>0.00017724556950660109</v>
       </c>
       <c r="Q6">
-        <v>-0.00026313424909580468</v>
+        <v>-0.00026326142874530389</v>
       </c>
       <c r="R6">
-        <v>-0.00023366268862189121</v>
+        <v>-0.00023376743133066147</v>
       </c>
       <c r="S6">
-        <v>0.00014051762578142467</v>
+        <v>0.00014054516612603844</v>
       </c>
       <c r="T6">
-        <v>-0.00055198371870283231</v>
+        <v>-0.00055210331818639907</v>
       </c>
       <c r="U6">
-        <v>-0.00039664521688407423</v>
+        <v>-0.00039680319285552435</v>
       </c>
       <c r="V6">
-        <v>-1.3583423428414898e-07</v>
+        <v>-2.9916415842864974e-07</v>
       </c>
       <c r="W6">
-        <v>-7.7953170142740572e-05</v>
+        <v>-7.7964990227346112e-05</v>
       </c>
       <c r="X6">
-        <v>0.0008560236571222013</v>
+        <v>0.0008561282207184967</v>
       </c>
       <c r="Y6">
-        <v>0.16648058498717488</v>
+        <v>0.16650170403807674</v>
       </c>
     </row>
     <row r="7">
@@ -1019,76 +1019,76 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <v>0.049600750971164877</v>
+        <v>0.04960623478266897</v>
       </c>
       <c r="C7">
-        <v>0.00031958539627207933</v>
+        <v>0.00031967730147480588</v>
       </c>
       <c r="D7">
-        <v>0.00032547362057806784</v>
+        <v>0.00032557029444143723</v>
       </c>
       <c r="E7">
-        <v>-2.2156233001565425e-06</v>
+        <v>-2.2163410276575095e-06</v>
       </c>
       <c r="F7">
-        <v>8.9683230638598621e-05</v>
+        <v>8.9646471711207071e-05</v>
       </c>
       <c r="G7">
-        <v>0.00022540557178631418</v>
+        <v>0.00022543583567750936</v>
       </c>
       <c r="H7">
-        <v>0.005080153272627873</v>
+        <v>0.0050805537555463787</v>
       </c>
       <c r="I7">
-        <v>0.0028961818460152369</v>
+        <v>0.0028965022173864036</v>
       </c>
       <c r="J7">
-        <v>-0.00022401512627251105</v>
+        <v>-0.00022404361070656404</v>
       </c>
       <c r="K7">
-        <v>0.00019015686889376372</v>
+        <v>0.00019018961101571421</v>
       </c>
       <c r="L7">
-        <v>-7.6137042227071659e-05</v>
+        <v>-7.6114521662576156e-05</v>
       </c>
       <c r="M7">
-        <v>0.00025630047841888881</v>
+        <v>0.00025633121703558395</v>
       </c>
       <c r="N7">
-        <v>0.00020210291150559183</v>
+        <v>0.00020213369778930752</v>
       </c>
       <c r="O7">
-        <v>0.0013911341897826204</v>
+        <v>0.0013913193622218099</v>
       </c>
       <c r="P7">
-        <v>-0.00040106203400793253</v>
+        <v>-0.00040115391401050445</v>
       </c>
       <c r="Q7">
-        <v>0.00071607032831221256</v>
+        <v>0.00071624881933539408</v>
       </c>
       <c r="R7">
-        <v>0.00038397096198027015</v>
+        <v>0.00038410221112102072</v>
       </c>
       <c r="S7">
-        <v>0.00062107566485741653</v>
+        <v>0.00062129832502369193</v>
       </c>
       <c r="T7">
-        <v>0.00051625243358947555</v>
+        <v>0.00051637967594370593</v>
       </c>
       <c r="U7">
-        <v>0.00039982679822226882</v>
+        <v>0.00039994738844769274</v>
       </c>
       <c r="V7">
-        <v>0.00072269423195278496</v>
+        <v>0.00072283373151140634</v>
       </c>
       <c r="W7">
-        <v>-5.7591349200144994e-05</v>
+        <v>-5.7591344688285846e-05</v>
       </c>
       <c r="X7">
-        <v>0.00037094442234440294</v>
+        <v>0.00037086542311981865</v>
       </c>
       <c r="Y7">
-        <v>-0.014598934105944851</v>
+        <v>-0.014602595817448792</v>
       </c>
     </row>
     <row r="8">
@@ -1096,76 +1096,76 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>0.02190821118229162</v>
+        <v>0.021854364301091622</v>
       </c>
       <c r="C8">
-        <v>9.2277019913184584e-05</v>
+        <v>9.202019046648082e-05</v>
       </c>
       <c r="D8">
-        <v>0.00071316978225839092</v>
+        <v>0.00071360480317597588</v>
       </c>
       <c r="E8">
-        <v>-5.4258089138335806e-06</v>
+        <v>-5.4288528804621259e-06</v>
       </c>
       <c r="F8">
-        <v>-0.00012653729951742228</v>
+        <v>-0.0001265523761466718</v>
       </c>
       <c r="G8">
-        <v>0.00043624020772464224</v>
+        <v>0.00043622779977941454</v>
       </c>
       <c r="H8">
-        <v>0.0028961818460152369</v>
+        <v>0.0028965022173864036</v>
       </c>
       <c r="I8">
-        <v>0.0042936496148311427</v>
+        <v>0.0042939896559333387</v>
       </c>
       <c r="J8">
-        <v>-0.00022714115484632059</v>
+        <v>-0.00022725836142650931</v>
       </c>
       <c r="K8">
-        <v>8.8253648770389133e-06</v>
+        <v>8.6165921000539098e-06</v>
       </c>
       <c r="L8">
-        <v>8.2962698213205578e-05</v>
+        <v>8.2616196208383074e-05</v>
       </c>
       <c r="M8">
-        <v>0.00058715040816659453</v>
+        <v>0.00058723759636325663</v>
       </c>
       <c r="N8">
-        <v>0.0009189425703166901</v>
+        <v>0.00091916946422159515</v>
       </c>
       <c r="O8">
-        <v>0.0021141789148999566</v>
+        <v>0.0021145539484863007</v>
       </c>
       <c r="P8">
-        <v>0.0001476503768315404</v>
+        <v>0.00014804630244966144</v>
       </c>
       <c r="Q8">
-        <v>0.0009215915984279201</v>
+        <v>0.00092164970538139682</v>
       </c>
       <c r="R8">
-        <v>0.00093785476767055962</v>
+        <v>0.00093795861874180087</v>
       </c>
       <c r="S8">
-        <v>0.0011607549993109239</v>
+        <v>0.0011602133432301888</v>
       </c>
       <c r="T8">
-        <v>0.00074951123555981212</v>
+        <v>0.00074961405640390174</v>
       </c>
       <c r="U8">
-        <v>0.0011488763990644686</v>
+        <v>0.0011489110652464554</v>
       </c>
       <c r="V8">
-        <v>0.00086127751849141021</v>
+        <v>0.00086136483622944961</v>
       </c>
       <c r="W8">
-        <v>2.6254312530237228e-05</v>
+        <v>2.6233599425287853e-05</v>
       </c>
       <c r="X8">
-        <v>6.8865382215900191e-05</v>
+        <v>6.9311461262675693e-05</v>
       </c>
       <c r="Y8">
-        <v>-0.028443720688763968</v>
+        <v>-0.028459061067412694</v>
       </c>
     </row>
     <row r="9">
@@ -1173,76 +1173,76 @@
         <v>23</v>
       </c>
       <c r="B9">
-        <v>-1.0337325884982158</v>
+        <v>-1.033770163177413</v>
       </c>
       <c r="C9">
-        <v>-7.2875167281320871e-05</v>
+        <v>-7.331760072023586e-05</v>
       </c>
       <c r="D9">
-        <v>0.0058492891862881313</v>
+        <v>0.0058494260028782857</v>
       </c>
       <c r="E9">
-        <v>-5.3022978022562901e-05</v>
+        <v>-5.3024057438836605e-05</v>
       </c>
       <c r="F9">
-        <v>-0.011854942445491623</v>
+        <v>-0.011855212437201654</v>
       </c>
       <c r="G9">
-        <v>-0.010471634473984352</v>
+        <v>-0.010471894121715189</v>
       </c>
       <c r="H9">
-        <v>-0.00022401512627251105</v>
+        <v>-0.00022404361070656404</v>
       </c>
       <c r="I9">
-        <v>-0.00022714115484632059</v>
+        <v>-0.00022725836142650931</v>
       </c>
       <c r="J9">
-        <v>0.016580473118586042</v>
+        <v>0.016580795905178934</v>
       </c>
       <c r="K9">
-        <v>-0.0023750698024248796</v>
+        <v>-0.0023754534627535113</v>
       </c>
       <c r="L9">
-        <v>8.3319313859200883e-05</v>
+        <v>8.3148213434212914e-05</v>
       </c>
       <c r="M9">
-        <v>-0.00036269770216627601</v>
+        <v>-0.00036269492924667548</v>
       </c>
       <c r="N9">
-        <v>-0.00094745685326783763</v>
+        <v>-0.00094747241147031744</v>
       </c>
       <c r="O9">
-        <v>-0.0020133703378150056</v>
+        <v>-0.0020133480897541242</v>
       </c>
       <c r="P9">
-        <v>-8.1927256903799317e-05</v>
+        <v>-8.1519956650927261e-05</v>
       </c>
       <c r="Q9">
-        <v>-0.00032505081919300544</v>
+        <v>-0.00032502564908160753</v>
       </c>
       <c r="R9">
-        <v>-0.0002158657726506405</v>
+        <v>-0.00021588199243713357</v>
       </c>
       <c r="S9">
-        <v>0.00010708941484083951</v>
+        <v>0.00010665282318286394</v>
       </c>
       <c r="T9">
-        <v>5.8503358031640473e-05</v>
+        <v>5.8516892856338987e-05</v>
       </c>
       <c r="U9">
-        <v>-0.00012000629166868809</v>
+        <v>-0.00011998153827468688</v>
       </c>
       <c r="V9">
-        <v>-0.00054107941612495207</v>
+        <v>-0.00054105670192655664</v>
       </c>
       <c r="W9">
-        <v>0.00012991590171457755</v>
+        <v>0.00012991010158539505</v>
       </c>
       <c r="X9">
-        <v>-0.00076411163723786452</v>
+        <v>-0.0007638186510975295</v>
       </c>
       <c r="Y9">
-        <v>-0.15992006007432602</v>
+        <v>-0.15992406178289431</v>
       </c>
     </row>
     <row r="10">
@@ -1250,76 +1250,76 @@
         <v>24</v>
       </c>
       <c r="B10">
-        <v>0.13809849870756685</v>
+        <v>0.13804408599137261</v>
       </c>
       <c r="C10">
-        <v>0.00011367285074757817</v>
+        <v>0.00011337716315218516</v>
       </c>
       <c r="D10">
-        <v>-0.00011695211600249583</v>
+        <v>-0.00011665190321906438</v>
       </c>
       <c r="E10">
-        <v>1.1189365428499978e-06</v>
+        <v>1.1169784064416069e-06</v>
       </c>
       <c r="F10">
-        <v>0.0017889662486112743</v>
+        <v>0.0017891674068608154</v>
       </c>
       <c r="G10">
-        <v>0.00019015271266200305</v>
+        <v>0.00019013702091490343</v>
       </c>
       <c r="H10">
-        <v>0.00019015686889376372</v>
+        <v>0.00019018961101571421</v>
       </c>
       <c r="I10">
-        <v>8.8253648770389133e-06</v>
+        <v>8.6165921000539098e-06</v>
       </c>
       <c r="J10">
-        <v>-0.0023750698024248796</v>
+        <v>-0.0023754534627535113</v>
       </c>
       <c r="K10">
-        <v>0.010046432457173174</v>
+        <v>0.010047054685614894</v>
       </c>
       <c r="L10">
-        <v>0.00022958968391110623</v>
+        <v>0.00022925265625620313</v>
       </c>
       <c r="M10">
-        <v>0.0036180455895945636</v>
+        <v>0.0036183057026887584</v>
       </c>
       <c r="N10">
-        <v>0.0086812526808428443</v>
+        <v>0.0086820930050419548</v>
       </c>
       <c r="O10">
-        <v>0.0086939372898196202</v>
+        <v>0.0086946667889408625</v>
       </c>
       <c r="P10">
-        <v>-0.0014813617118364878</v>
+        <v>-0.0014810764956219033</v>
       </c>
       <c r="Q10">
-        <v>-0.00015779242744860811</v>
+        <v>-0.00015793164134294754</v>
       </c>
       <c r="R10">
-        <v>-0.00066401838513888492</v>
+        <v>-0.00066416689999699782</v>
       </c>
       <c r="S10">
-        <v>-0.00092745899511592026</v>
+        <v>-0.00092843268530518248</v>
       </c>
       <c r="T10">
-        <v>-0.00049752945056342687</v>
+        <v>-0.00049762042177596382</v>
       </c>
       <c r="U10">
-        <v>-0.00029326280586914211</v>
+        <v>-0.00029336562375335655</v>
       </c>
       <c r="V10">
-        <v>-0.00036654459478288951</v>
+        <v>-0.00036664292016380662</v>
       </c>
       <c r="W10">
-        <v>4.1880366462488609e-05</v>
+        <v>4.1844362811155984e-05</v>
       </c>
       <c r="X10">
-        <v>-0.00018097421900054901</v>
+        <v>-0.00018034555545380811</v>
       </c>
       <c r="Y10">
-        <v>-0.0060027937355755789</v>
+        <v>-0.0060137935834939371</v>
       </c>
     </row>
     <row r="11">
@@ -1327,76 +1327,76 @@
         <v>25</v>
       </c>
       <c r="B11">
-        <v>0.16195831250086346</v>
+        <v>0.16187379552959719</v>
       </c>
       <c r="C11">
-        <v>-0.00019337528582403249</v>
+        <v>-0.00019397742251601774</v>
       </c>
       <c r="D11">
-        <v>0.00050319387980053698</v>
+        <v>0.00050380571806615815</v>
       </c>
       <c r="E11">
-        <v>-4.1832564008674944e-06</v>
+        <v>-4.1874440949755346e-06</v>
       </c>
       <c r="F11">
-        <v>-0.00026379697373673378</v>
+        <v>-0.00026378356889011217</v>
       </c>
       <c r="G11">
-        <v>-0.00019007480181538333</v>
+        <v>-0.00019010366840431503</v>
       </c>
       <c r="H11">
-        <v>-7.6137042227071659e-05</v>
+        <v>-7.6114521662576156e-05</v>
       </c>
       <c r="I11">
-        <v>8.2962698213205578e-05</v>
+        <v>8.2616196208383074e-05</v>
       </c>
       <c r="J11">
-        <v>8.3319313859200883e-05</v>
+        <v>8.3148213434212914e-05</v>
       </c>
       <c r="K11">
-        <v>0.00022958968391110623</v>
+        <v>0.00022925265625620313</v>
       </c>
       <c r="L11">
-        <v>0.0037259722287291473</v>
+        <v>0.0037257057413935513</v>
       </c>
       <c r="M11">
-        <v>0.0015812283537065348</v>
+        <v>0.001581350863737784</v>
       </c>
       <c r="N11">
-        <v>0.0016901321808523938</v>
+        <v>0.0016904372280317792</v>
       </c>
       <c r="O11">
-        <v>0.0016526272983173967</v>
+        <v>0.0016528887520674488</v>
       </c>
       <c r="P11">
-        <v>0.00051746781389917502</v>
+        <v>0.00051824689684483254</v>
       </c>
       <c r="Q11">
-        <v>0.00018064402922648559</v>
+        <v>0.00018061883562657446</v>
       </c>
       <c r="R11">
-        <v>0.0002457055645072538</v>
+        <v>0.00024575039570695059</v>
       </c>
       <c r="S11">
-        <v>0.00028312943050623761</v>
+        <v>0.00028181945827751109</v>
       </c>
       <c r="T11">
-        <v>9.400923045754404e-05</v>
+        <v>9.4085157568694899e-05</v>
       </c>
       <c r="U11">
-        <v>0.00066740216175676281</v>
+        <v>0.00066737962189110682</v>
       </c>
       <c r="V11">
-        <v>0.00022231884965593773</v>
+        <v>0.00022238624859621223</v>
       </c>
       <c r="W11">
-        <v>-2.6329307756217495e-05</v>
+        <v>-2.6400060074644198e-05</v>
       </c>
       <c r="X11">
-        <v>0.00040170218584037703</v>
+        <v>0.00040281613969062177</v>
       </c>
       <c r="Y11">
-        <v>-0.016766972410609253</v>
+        <v>-0.016787752027816405</v>
       </c>
     </row>
     <row r="12">
@@ -1404,76 +1404,76 @@
         <v>26</v>
       </c>
       <c r="B12">
-        <v>0.031295741376551979</v>
+        <v>0.031297148679227234</v>
       </c>
       <c r="C12">
-        <v>-5.7941091450655506e-05</v>
+        <v>-5.7890159434744083e-05</v>
       </c>
       <c r="D12">
-        <v>0.00029895339810032118</v>
+        <v>0.00029900318018807794</v>
       </c>
       <c r="E12">
-        <v>-2.2549450359362003e-06</v>
+        <v>-2.2553300544623354e-06</v>
       </c>
       <c r="F12">
-        <v>0.00018873691483347818</v>
+        <v>0.00018874269157246291</v>
       </c>
       <c r="G12">
-        <v>0.00022282598577271374</v>
+        <v>0.0002227411949269377</v>
       </c>
       <c r="H12">
-        <v>0.00025630047841888881</v>
+        <v>0.00025633121703558395</v>
       </c>
       <c r="I12">
-        <v>0.00058715040816659453</v>
+        <v>0.00058723759636325663</v>
       </c>
       <c r="J12">
-        <v>-0.00036269770216627601</v>
+        <v>-0.00036269492924667548</v>
       </c>
       <c r="K12">
-        <v>0.0036180455895945636</v>
+        <v>0.0036183057026887584</v>
       </c>
       <c r="L12">
-        <v>0.0015812283537065348</v>
+        <v>0.001581350863737784</v>
       </c>
       <c r="M12">
-        <v>0.0057121303464280062</v>
+        <v>0.0057124422353091514</v>
       </c>
       <c r="N12">
-        <v>0.0051154805745930914</v>
+        <v>0.0051158356225267333</v>
       </c>
       <c r="O12">
-        <v>0.0052507375929707837</v>
+        <v>0.0052510710657778722</v>
       </c>
       <c r="P12">
-        <v>0.00050147579781648641</v>
+        <v>0.00050150019614737113</v>
       </c>
       <c r="Q12">
-        <v>-0.00031756108121901508</v>
+        <v>-0.0003175935004988209</v>
       </c>
       <c r="R12">
-        <v>-0.00041960833954922741</v>
+        <v>-0.00041962949842579232</v>
       </c>
       <c r="S12">
-        <v>-0.00032537621366163835</v>
+        <v>-0.00032529913164938159</v>
       </c>
       <c r="T12">
-        <v>-0.00027766656221246255</v>
+        <v>-0.00027769854888019547</v>
       </c>
       <c r="U12">
-        <v>-0.00020694007130019456</v>
+        <v>-0.00020693714069744689</v>
       </c>
       <c r="V12">
-        <v>-0.00030318246631905557</v>
+        <v>-0.00030323731948758768</v>
       </c>
       <c r="W12">
-        <v>2.2234038349129201e-05</v>
+        <v>2.2241903466405089e-05</v>
       </c>
       <c r="X12">
-        <v>0.00016975790142951044</v>
+        <v>0.00016971353593052494</v>
       </c>
       <c r="Y12">
-        <v>-0.015544252096871589</v>
+        <v>-0.015546372834418024</v>
       </c>
     </row>
     <row r="13">
@@ -1481,76 +1481,76 @@
         <v>27</v>
       </c>
       <c r="B13">
-        <v>-0.011064354113368192</v>
+        <v>-0.011056684234813732</v>
       </c>
       <c r="C13">
-        <v>-0.00044511384326082338</v>
+        <v>-0.00044495405509703144</v>
       </c>
       <c r="D13">
-        <v>0.00037288580278485584</v>
+        <v>0.00037284900316576081</v>
       </c>
       <c r="E13">
-        <v>-2.578212703962233e-06</v>
+        <v>-2.5780367690972491e-06</v>
       </c>
       <c r="F13">
-        <v>0.00063675129607465575</v>
+        <v>0.0006368582083605169</v>
       </c>
       <c r="G13">
-        <v>-8.4400786173235987e-05</v>
+        <v>-8.4553526749065605e-05</v>
       </c>
       <c r="H13">
-        <v>0.00020210291150559183</v>
+        <v>0.00020213369778930752</v>
       </c>
       <c r="I13">
-        <v>0.0009189425703166901</v>
+        <v>0.00091916946422159515</v>
       </c>
       <c r="J13">
-        <v>-0.00094745685326783763</v>
+        <v>-0.00094747241147031744</v>
       </c>
       <c r="K13">
-        <v>0.0086812526808428443</v>
+        <v>0.0086820930050419548</v>
       </c>
       <c r="L13">
-        <v>0.0016901321808523938</v>
+        <v>0.0016904372280317792</v>
       </c>
       <c r="M13">
-        <v>0.0051154805745930914</v>
+        <v>0.0051158356225267333</v>
       </c>
       <c r="N13">
-        <v>0.013645364278491339</v>
+        <v>0.013646372490531199</v>
       </c>
       <c r="O13">
-        <v>0.010588068513824191</v>
+        <v>0.010588892432423249</v>
       </c>
       <c r="P13">
-        <v>0.00059303654177134905</v>
+        <v>0.00059286625073840058</v>
       </c>
       <c r="Q13">
-        <v>-0.00046905901832576796</v>
+        <v>-0.00046912881963381402</v>
       </c>
       <c r="R13">
-        <v>-0.00071658041887770734</v>
+        <v>-0.00071667185048940579</v>
       </c>
       <c r="S13">
-        <v>-0.0014947499067584993</v>
+        <v>-0.0014945102424165509</v>
       </c>
       <c r="T13">
-        <v>-0.00057221584141210844</v>
+        <v>-0.00057233937837377919</v>
       </c>
       <c r="U13">
-        <v>-0.00060552285209864668</v>
+        <v>-0.00060557999574334734</v>
       </c>
       <c r="V13">
-        <v>-0.00049098548314260252</v>
+        <v>-0.00049110413306726599</v>
       </c>
       <c r="W13">
-        <v>6.5166316608058637e-05</v>
+        <v>6.5200146862335402e-05</v>
       </c>
       <c r="X13">
-        <v>-7.823868714326894e-05</v>
+        <v>-7.8600624646599053e-05</v>
       </c>
       <c r="Y13">
-        <v>-0.024154787573449715</v>
+        <v>-0.024154563808679808</v>
       </c>
     </row>
     <row r="14">
@@ -1558,76 +1558,76 @@
         <v>28</v>
       </c>
       <c r="B14">
-        <v>0.26834061865294839</v>
+        <v>0.26833953350676221</v>
       </c>
       <c r="C14">
-        <v>-0.00074793070381997924</v>
+        <v>-0.00074780033940842635</v>
       </c>
       <c r="D14">
-        <v>0.00060563612340472361</v>
+        <v>0.00060577660682216081</v>
       </c>
       <c r="E14">
-        <v>-3.8693355835524149e-06</v>
+        <v>-3.8704749348174414e-06</v>
       </c>
       <c r="F14">
-        <v>0.0013453403113298928</v>
+        <v>0.0013453521981434576</v>
       </c>
       <c r="G14">
-        <v>0.00026693663249364487</v>
+        <v>0.00026676730403549578</v>
       </c>
       <c r="H14">
-        <v>0.0013911341897826204</v>
+        <v>0.0013913193622218099</v>
       </c>
       <c r="I14">
-        <v>0.0021141789148999566</v>
+        <v>0.0021145539484863007</v>
       </c>
       <c r="J14">
-        <v>-0.0020133703378150056</v>
+        <v>-0.0020133480897541242</v>
       </c>
       <c r="K14">
-        <v>0.0086939372898196202</v>
+        <v>0.0086946667889408625</v>
       </c>
       <c r="L14">
-        <v>0.0016526272983173967</v>
+        <v>0.0016528887520674488</v>
       </c>
       <c r="M14">
-        <v>0.0052507375929707837</v>
+        <v>0.0052510710657778722</v>
       </c>
       <c r="N14">
-        <v>0.010588068513824191</v>
+        <v>0.010588892432423249</v>
       </c>
       <c r="O14">
-        <v>0.013409844178573806</v>
+        <v>0.013410811607106271</v>
       </c>
       <c r="P14">
-        <v>0.00071305383428605165</v>
+        <v>0.00071294352084205759</v>
       </c>
       <c r="Q14">
-        <v>0.00032182124432197055</v>
+        <v>0.00032185812934484859</v>
       </c>
       <c r="R14">
-        <v>-0.00027623885150632188</v>
+        <v>-0.00027619838523818517</v>
       </c>
       <c r="S14">
-        <v>-0.00050806908763307798</v>
+        <v>-0.00050768375328096396</v>
       </c>
       <c r="T14">
-        <v>-1.5760250379026619e-05</v>
+        <v>-1.5741621053791399e-05</v>
       </c>
       <c r="U14">
-        <v>0.00021922550568397123</v>
+        <v>0.00021926810676775339</v>
       </c>
       <c r="V14">
-        <v>0.00014198655100670964</v>
+        <v>0.00014195395439349588</v>
       </c>
       <c r="W14">
-        <v>5.4496578314349765e-05</v>
+        <v>5.4530800481503681e-05</v>
       </c>
       <c r="X14">
-        <v>-5.4112602704414412e-05</v>
+        <v>-5.4496344426982826e-05</v>
       </c>
       <c r="Y14">
-        <v>-0.034910163465996208</v>
+        <v>-0.034916024665207573</v>
       </c>
     </row>
     <row r="15">
@@ -1635,76 +1635,76 @@
         <v>29</v>
       </c>
       <c r="B15">
-        <v>0.46795453514104168</v>
+        <v>0.46805363414889128</v>
       </c>
       <c r="C15">
-        <v>-0.0015540246346103083</v>
+        <v>-0.001553361962015571</v>
       </c>
       <c r="D15">
-        <v>-0.00050893754970762761</v>
+        <v>-0.00050972634126932037</v>
       </c>
       <c r="E15">
-        <v>4.2255046483836902e-06</v>
+        <v>4.2309286353634087e-06</v>
       </c>
       <c r="F15">
-        <v>9.1703187757349869e-05</v>
+        <v>9.1680635442258074e-05</v>
       </c>
       <c r="G15">
-        <v>0.00017720029612834642</v>
+        <v>0.00017724556950660109</v>
       </c>
       <c r="H15">
-        <v>-0.00040106203400793253</v>
+        <v>-0.00040115391401050445</v>
       </c>
       <c r="I15">
-        <v>0.0001476503768315404</v>
+        <v>0.00014804630244966144</v>
       </c>
       <c r="J15">
-        <v>-8.1927256903799317e-05</v>
+        <v>-8.1519956650927261e-05</v>
       </c>
       <c r="K15">
-        <v>-0.0014813617118364878</v>
+        <v>-0.0014810764956219033</v>
       </c>
       <c r="L15">
-        <v>0.00051746781389917502</v>
+        <v>0.00051824689684483254</v>
       </c>
       <c r="M15">
-        <v>0.00050147579781648641</v>
+        <v>0.00050150019614737113</v>
       </c>
       <c r="N15">
-        <v>0.00059303654177134905</v>
+        <v>0.00059286625073840058</v>
       </c>
       <c r="O15">
-        <v>0.00071305383428605165</v>
+        <v>0.00071294352084205759</v>
       </c>
       <c r="P15">
-        <v>0.0061687200247080021</v>
+        <v>0.006168178004862801</v>
       </c>
       <c r="Q15">
-        <v>-0.00070860473292364435</v>
+        <v>-0.00070848439702978503</v>
       </c>
       <c r="R15">
-        <v>-0.00023266518961132876</v>
+        <v>-0.0002325408938903858</v>
       </c>
       <c r="S15">
-        <v>-0.00046128882818035016</v>
+        <v>-0.00045953681704153369</v>
       </c>
       <c r="T15">
-        <v>-0.00041505052783768017</v>
+        <v>-0.0004150214162990573</v>
       </c>
       <c r="U15">
-        <v>-0.00015095874068804765</v>
+        <v>-0.00015085902177469494</v>
       </c>
       <c r="V15">
-        <v>-0.00051687455332126843</v>
+        <v>-0.00051684723191767741</v>
       </c>
       <c r="W15">
-        <v>5.0756281960641033e-05</v>
+        <v>5.0843511466612946e-05</v>
       </c>
       <c r="X15">
-        <v>0.00013244538250348713</v>
+        <v>0.00013112722604240071</v>
       </c>
       <c r="Y15">
-        <v>0.01484495010740073</v>
+        <v>0.014871309672353936</v>
       </c>
     </row>
     <row r="16">
@@ -1712,76 +1712,76 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>-0.025913316858195281</v>
+        <v>-0.025917432865169447</v>
       </c>
       <c r="C16">
-        <v>0.00037473684200277379</v>
+        <v>0.00037471880904776087</v>
       </c>
       <c r="D16">
-        <v>0.00081544929062930816</v>
+        <v>0.0008158134524309385</v>
       </c>
       <c r="E16">
-        <v>-6.0028054226119202e-06</v>
+        <v>-6.0054923637039605e-06</v>
       </c>
       <c r="F16">
-        <v>-0.00027253493038349036</v>
+        <v>-0.00027265044014394141</v>
       </c>
       <c r="G16">
-        <v>-0.00026313424909580468</v>
+        <v>-0.00026326142874530389</v>
       </c>
       <c r="H16">
-        <v>0.00071607032831221256</v>
+        <v>0.00071624881933539408</v>
       </c>
       <c r="I16">
-        <v>0.0009215915984279201</v>
+        <v>0.00092164970538139682</v>
       </c>
       <c r="J16">
-        <v>-0.00032505081919300544</v>
+        <v>-0.00032502564908160753</v>
       </c>
       <c r="K16">
-        <v>-0.00015779242744860811</v>
+        <v>-0.00015793164134294754</v>
       </c>
       <c r="L16">
-        <v>0.00018064402922648559</v>
+        <v>0.00018061883562657446</v>
       </c>
       <c r="M16">
-        <v>-0.00031756108121901508</v>
+        <v>-0.0003175935004988209</v>
       </c>
       <c r="N16">
-        <v>-0.00046905901832576796</v>
+        <v>-0.00046912881963381402</v>
       </c>
       <c r="O16">
-        <v>0.00032182124432197055</v>
+        <v>0.00032185812934484859</v>
       </c>
       <c r="P16">
-        <v>-0.00070860473292364435</v>
+        <v>-0.00070848439702978503</v>
       </c>
       <c r="Q16">
-        <v>0.012075237990345204</v>
+        <v>0.012075948034216237</v>
       </c>
       <c r="R16">
-        <v>0.0090986881789409651</v>
+        <v>0.0090992433862796054</v>
       </c>
       <c r="S16">
-        <v>0.009152513979631724</v>
+        <v>0.0091529282177041718</v>
       </c>
       <c r="T16">
-        <v>0.0090699326156811096</v>
+        <v>0.0090704919941855238</v>
       </c>
       <c r="U16">
-        <v>0.0091547272755910514</v>
+        <v>0.0091552732052523622</v>
       </c>
       <c r="V16">
-        <v>0.0090829188293393929</v>
+        <v>0.0090834763367899415</v>
       </c>
       <c r="W16">
-        <v>-9.3325764638094708e-05</v>
+        <v>-9.3347218570766438e-05</v>
       </c>
       <c r="X16">
-        <v>0.00032880682921118329</v>
+        <v>0.00032897643488462736</v>
       </c>
       <c r="Y16">
-        <v>-0.035531996191273785</v>
+        <v>-0.035544470176122403</v>
       </c>
     </row>
     <row r="17">
@@ -1789,76 +1789,76 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>0.035281756633913419</v>
+        <v>0.035274411052925378</v>
       </c>
       <c r="C17">
-        <v>0.00044966432280574709</v>
+        <v>0.00044969172702185364</v>
       </c>
       <c r="D17">
-        <v>0.0014438308230710073</v>
+        <v>0.0014442747913062243</v>
       </c>
       <c r="E17">
-        <v>-1.0773862347420956e-05</v>
+        <v>-1.077712555550578e-05</v>
       </c>
       <c r="F17">
-        <v>-0.00038707854340498671</v>
+        <v>-0.00038716513852304207</v>
       </c>
       <c r="G17">
-        <v>-0.00023366268862189121</v>
+        <v>-0.00023376743133066147</v>
       </c>
       <c r="H17">
-        <v>0.00038397096198027015</v>
+        <v>0.00038410221112102072</v>
       </c>
       <c r="I17">
-        <v>0.00093785476767055962</v>
+        <v>0.00093795861874180087</v>
       </c>
       <c r="J17">
-        <v>-0.0002158657726506405</v>
+        <v>-0.00021588199243713357</v>
       </c>
       <c r="K17">
-        <v>-0.00066401838513888492</v>
+        <v>-0.00066416689999699782</v>
       </c>
       <c r="L17">
-        <v>0.0002457055645072538</v>
+        <v>0.00024575039570695059</v>
       </c>
       <c r="M17">
-        <v>-0.00041960833954922741</v>
+        <v>-0.00041962949842579232</v>
       </c>
       <c r="N17">
-        <v>-0.00071658041887770734</v>
+        <v>-0.00071667185048940579</v>
       </c>
       <c r="O17">
-        <v>-0.00027623885150632188</v>
+        <v>-0.00027619838523818517</v>
       </c>
       <c r="P17">
-        <v>-0.00023266518961132876</v>
+        <v>-0.0002325408938903858</v>
       </c>
       <c r="Q17">
-        <v>0.0090986881789409651</v>
+        <v>0.0090992433862796054</v>
       </c>
       <c r="R17">
-        <v>0.012319275401630296</v>
+        <v>0.012319996239166603</v>
       </c>
       <c r="S17">
-        <v>0.0091992553621125031</v>
+        <v>0.0091997588140308763</v>
       </c>
       <c r="T17">
-        <v>0.0090017974790533792</v>
+        <v>0.0090023513306020011</v>
       </c>
       <c r="U17">
-        <v>0.0091454367776697548</v>
+        <v>0.0091459742295460101</v>
       </c>
       <c r="V17">
-        <v>0.0090494880791689367</v>
+        <v>0.009050041919103656</v>
       </c>
       <c r="W17">
-        <v>-7.3405906387087367e-05</v>
+        <v>-7.3419817233912727e-05</v>
       </c>
       <c r="X17">
-        <v>0.00029141810043692863</v>
+        <v>0.00029153687380506239</v>
       </c>
       <c r="Y17">
-        <v>-0.055972733833845739</v>
+        <v>-0.055988083672354416</v>
       </c>
     </row>
     <row r="18">
@@ -1866,76 +1866,76 @@
         <v>32</v>
       </c>
       <c r="B18">
-        <v>0.11915790468246124</v>
+        <v>0.11899269376577361</v>
       </c>
       <c r="C18">
-        <v>0.00083209192765267438</v>
+        <v>0.0008309067437706273</v>
       </c>
       <c r="D18">
-        <v>0.0014061250129435076</v>
+        <v>0.001407541414986945</v>
       </c>
       <c r="E18">
-        <v>-1.0675723241624991e-05</v>
+        <v>-1.0685400757698298e-05</v>
       </c>
       <c r="F18">
-        <v>-0.00061029048194654071</v>
+        <v>-0.00061038663719111853</v>
       </c>
       <c r="G18">
-        <v>0.00014051762578142467</v>
+        <v>0.00014054516612603844</v>
       </c>
       <c r="H18">
-        <v>0.00062107566485741653</v>
+        <v>0.00062129832502369193</v>
       </c>
       <c r="I18">
-        <v>0.0011607549993109239</v>
+        <v>0.0011602133432301888</v>
       </c>
       <c r="J18">
-        <v>0.00010708941484083951</v>
+        <v>0.00010665282318286394</v>
       </c>
       <c r="K18">
-        <v>-0.00092745899511592026</v>
+        <v>-0.00092843268530518248</v>
       </c>
       <c r="L18">
-        <v>0.00028312943050623761</v>
+        <v>0.00028181945827751109</v>
       </c>
       <c r="M18">
-        <v>-0.00032537621366163835</v>
+        <v>-0.00032529913164938159</v>
       </c>
       <c r="N18">
-        <v>-0.0014947499067584993</v>
+        <v>-0.0014945102424165509</v>
       </c>
       <c r="O18">
-        <v>-0.00050806908763307798</v>
+        <v>-0.00050768375328096396</v>
       </c>
       <c r="P18">
-        <v>-0.00046128882818035016</v>
+        <v>-0.00045953681704153369</v>
       </c>
       <c r="Q18">
-        <v>0.009152513979631724</v>
+        <v>0.0091529282177041718</v>
       </c>
       <c r="R18">
-        <v>0.0091992553621125031</v>
+        <v>0.0091997588140308763</v>
       </c>
       <c r="S18">
-        <v>0.012602162345021968</v>
+        <v>0.012600880563958963</v>
       </c>
       <c r="T18">
-        <v>0.0090445383081104308</v>
+        <v>0.0090451570456724292</v>
       </c>
       <c r="U18">
-        <v>0.0092432011230562522</v>
+        <v>0.0092434957487699532</v>
       </c>
       <c r="V18">
-        <v>0.0090666200942843348</v>
+        <v>0.0090671946737533524</v>
       </c>
       <c r="W18">
-        <v>-0.00013019832926160603</v>
+        <v>-0.00013035026285169256</v>
       </c>
       <c r="X18">
-        <v>0.00038933629810280601</v>
+        <v>0.00039156635859698401</v>
       </c>
       <c r="Y18">
-        <v>-0.053228862965667229</v>
+        <v>-0.053277359124532006</v>
       </c>
     </row>
     <row r="19">
@@ -1943,76 +1943,76 @@
         <v>33</v>
       </c>
       <c r="B19">
-        <v>0.013453782948559726</v>
+        <v>0.01345626889885025</v>
       </c>
       <c r="C19">
-        <v>0.00051636486182710995</v>
+        <v>0.00051643597614740725</v>
       </c>
       <c r="D19">
-        <v>0.0012629612017679426</v>
+        <v>0.001263294423463554</v>
       </c>
       <c r="E19">
-        <v>-9.5137999705481938e-06</v>
+        <v>-9.5162780795942856e-06</v>
       </c>
       <c r="F19">
-        <v>-0.00055778335818701397</v>
+        <v>-0.00055785807744340721</v>
       </c>
       <c r="G19">
-        <v>-0.00055198371870283231</v>
+        <v>-0.00055210331818639907</v>
       </c>
       <c r="H19">
-        <v>0.00051625243358947555</v>
+        <v>0.00051637967594370593</v>
       </c>
       <c r="I19">
-        <v>0.00074951123555981212</v>
+        <v>0.00074961405640390174</v>
       </c>
       <c r="J19">
-        <v>5.8503358031640473e-05</v>
+        <v>5.8516892856338987e-05</v>
       </c>
       <c r="K19">
-        <v>-0.00049752945056342687</v>
+        <v>-0.00049762042177596382</v>
       </c>
       <c r="L19">
-        <v>9.400923045754404e-05</v>
+        <v>9.4085157568694899e-05</v>
       </c>
       <c r="M19">
-        <v>-0.00027766656221246255</v>
+        <v>-0.00027769854888019547</v>
       </c>
       <c r="N19">
-        <v>-0.00057221584141210844</v>
+        <v>-0.00057233937837377919</v>
       </c>
       <c r="O19">
-        <v>-1.5760250379026619e-05</v>
+        <v>-1.5741621053791399e-05</v>
       </c>
       <c r="P19">
-        <v>-0.00041505052783768017</v>
+        <v>-0.0004150214162990573</v>
       </c>
       <c r="Q19">
-        <v>0.0090699326156811096</v>
+        <v>0.0090704919941855238</v>
       </c>
       <c r="R19">
-        <v>0.0090017974790533792</v>
+        <v>0.0090023513306020011</v>
       </c>
       <c r="S19">
-        <v>0.0090445383081104308</v>
+        <v>0.0090451570456724292</v>
       </c>
       <c r="T19">
-        <v>0.01118989239300063</v>
+        <v>0.011190532690968983</v>
       </c>
       <c r="U19">
-        <v>0.0090510845392375687</v>
+        <v>0.0090516311242653039</v>
       </c>
       <c r="V19">
-        <v>0.0089920949264979018</v>
+        <v>0.0089926376723614993</v>
       </c>
       <c r="W19">
-        <v>-0.00010625516236494319</v>
+        <v>-0.0001062652756716239</v>
       </c>
       <c r="X19">
-        <v>0.00049932194704069895</v>
+        <v>0.00049934655680046892</v>
       </c>
       <c r="Y19">
-        <v>-0.049229459033065845</v>
+        <v>-0.049241013287212226</v>
       </c>
     </row>
     <row r="20">
@@ -2020,76 +2020,76 @@
         <v>34</v>
       </c>
       <c r="B20">
-        <v>0.013913329566552706</v>
+        <v>0.013903899726750308</v>
       </c>
       <c r="C20">
-        <v>0.00017084223439435857</v>
+        <v>0.00017082526894713008</v>
       </c>
       <c r="D20">
-        <v>0.0015359531350203626</v>
+        <v>0.0015363959200552016</v>
       </c>
       <c r="E20">
-        <v>-1.1756102432024641e-05</v>
+        <v>-1.1759368423350442e-05</v>
       </c>
       <c r="F20">
-        <v>-0.00045355422815356386</v>
+        <v>-0.00045367507191610562</v>
       </c>
       <c r="G20">
-        <v>-0.00039664521688407423</v>
+        <v>-0.00039680319285552435</v>
       </c>
       <c r="H20">
-        <v>0.00039982679822226882</v>
+        <v>0.00039994738844769274</v>
       </c>
       <c r="I20">
-        <v>0.0011488763990644686</v>
+        <v>0.0011489110652464554</v>
       </c>
       <c r="J20">
-        <v>-0.00012000629166868809</v>
+        <v>-0.00011998153827468688</v>
       </c>
       <c r="K20">
-        <v>-0.00029326280586914211</v>
+        <v>-0.00029336562375335655</v>
       </c>
       <c r="L20">
-        <v>0.00066740216175676281</v>
+        <v>0.00066737962189110682</v>
       </c>
       <c r="M20">
-        <v>-0.00020694007130019456</v>
+        <v>-0.00020693714069744689</v>
       </c>
       <c r="N20">
-        <v>-0.00060552285209864668</v>
+        <v>-0.00060557999574334734</v>
       </c>
       <c r="O20">
-        <v>0.00021922550568397123</v>
+        <v>0.00021926810676775339</v>
       </c>
       <c r="P20">
-        <v>-0.00015095874068804765</v>
+        <v>-0.00015085902177469494</v>
       </c>
       <c r="Q20">
-        <v>0.0091547272755910514</v>
+        <v>0.0091552732052523622</v>
       </c>
       <c r="R20">
-        <v>0.0091454367776697548</v>
+        <v>0.0091459742295460101</v>
       </c>
       <c r="S20">
-        <v>0.0092432011230562522</v>
+        <v>0.0092434957487699532</v>
       </c>
       <c r="T20">
-        <v>0.0090510845392375687</v>
+        <v>0.0090516311242653039</v>
       </c>
       <c r="U20">
-        <v>0.011363421947333576</v>
+        <v>0.011364039921707984</v>
       </c>
       <c r="V20">
-        <v>0.0090623684842705381</v>
+        <v>0.0090629107026245735</v>
       </c>
       <c r="W20">
-        <v>-9.846589372160177e-05</v>
+        <v>-9.8489935979540616e-05</v>
       </c>
       <c r="X20">
-        <v>0.00037416261987828752</v>
+        <v>0.00037435262496879253</v>
       </c>
       <c r="Y20">
-        <v>-0.058015549226256874</v>
+        <v>-0.058030625533849134</v>
       </c>
     </row>
     <row r="21">
@@ -2097,76 +2097,76 @@
         <v>35</v>
       </c>
       <c r="B21">
-        <v>-0.088602525221107745</v>
+        <v>-0.088597285494387904</v>
       </c>
       <c r="C21">
-        <v>0.00073688752101665222</v>
+        <v>0.00073700127852097672</v>
       </c>
       <c r="D21">
-        <v>0.001311178040704606</v>
+        <v>0.0013115773147099365</v>
       </c>
       <c r="E21">
-        <v>-9.5504226583854651e-06</v>
+        <v>-9.5534058688779026e-06</v>
       </c>
       <c r="F21">
-        <v>-0.00030286210280648825</v>
+        <v>-0.00030297118443714348</v>
       </c>
       <c r="G21">
-        <v>-1.3583423428414898e-07</v>
+        <v>-2.9916415842864974e-07</v>
       </c>
       <c r="H21">
-        <v>0.00072269423195278496</v>
+        <v>0.00072283373151140634</v>
       </c>
       <c r="I21">
-        <v>0.00086127751849141021</v>
+        <v>0.00086136483622944961</v>
       </c>
       <c r="J21">
-        <v>-0.00054107941612495207</v>
+        <v>-0.00054105670192655664</v>
       </c>
       <c r="K21">
-        <v>-0.00036654459478288951</v>
+        <v>-0.00036664292016380662</v>
       </c>
       <c r="L21">
-        <v>0.00022231884965593773</v>
+        <v>0.00022238624859621223</v>
       </c>
       <c r="M21">
-        <v>-0.00030318246631905557</v>
+        <v>-0.00030323731948758768</v>
       </c>
       <c r="N21">
-        <v>-0.00049098548314260252</v>
+        <v>-0.00049110413306726599</v>
       </c>
       <c r="O21">
-        <v>0.00014198655100670964</v>
+        <v>0.00014195395439349588</v>
       </c>
       <c r="P21">
-        <v>-0.00051687455332126843</v>
+        <v>-0.00051684723191767741</v>
       </c>
       <c r="Q21">
-        <v>0.0090829188293393929</v>
+        <v>0.0090834763367899415</v>
       </c>
       <c r="R21">
-        <v>0.0090494880791689367</v>
+        <v>0.009050041919103656</v>
       </c>
       <c r="S21">
-        <v>0.0090666200942843348</v>
+        <v>0.0090671946737533524</v>
       </c>
       <c r="T21">
-        <v>0.0089920949264979018</v>
+        <v>0.0089926376723614993</v>
       </c>
       <c r="U21">
-        <v>0.0090623684842705381</v>
+        <v>0.0090629107026245735</v>
       </c>
       <c r="V21">
-        <v>0.011580911401719345</v>
+        <v>0.011581568265054531</v>
       </c>
       <c r="W21">
-        <v>-0.00010800137532225124</v>
+        <v>-0.00010801340622833765</v>
       </c>
       <c r="X21">
-        <v>0.00040621572446263542</v>
+        <v>0.00040624947794898119</v>
       </c>
       <c r="Y21">
-        <v>-0.052227684954312625</v>
+        <v>-0.052241337165325003</v>
       </c>
     </row>
     <row r="22">
@@ -2174,76 +2174,76 @@
         <v>36</v>
       </c>
       <c r="B22">
-        <v>-0.040132273368803997</v>
+        <v>-0.040144177783449593</v>
       </c>
       <c r="C22">
-        <v>-7.9075494791071407e-05</v>
+        <v>-7.9151029552920537e-05</v>
       </c>
       <c r="D22">
-        <v>-6.0076720498855943e-05</v>
+        <v>-6.0050833899493589e-05</v>
       </c>
       <c r="E22">
-        <v>3.8261469408698318e-07</v>
+        <v>3.8245581064729384e-07</v>
       </c>
       <c r="F22">
-        <v>-6.8679618888095595e-05</v>
+        <v>-6.8673621271978305e-05</v>
       </c>
       <c r="G22">
-        <v>-7.7953170142740572e-05</v>
+        <v>-7.7964990227346112e-05</v>
       </c>
       <c r="H22">
-        <v>-5.7591349200144994e-05</v>
+        <v>-5.7591344688285846e-05</v>
       </c>
       <c r="I22">
-        <v>2.6254312530237228e-05</v>
+        <v>2.6233599425287853e-05</v>
       </c>
       <c r="J22">
-        <v>0.00012991590171457755</v>
+        <v>0.00012991010158539505</v>
       </c>
       <c r="K22">
-        <v>4.1880366462488609e-05</v>
+        <v>4.1844362811155984e-05</v>
       </c>
       <c r="L22">
-        <v>-2.6329307756217495e-05</v>
+        <v>-2.6400060074644198e-05</v>
       </c>
       <c r="M22">
-        <v>2.2234038349129201e-05</v>
+        <v>2.2241903466405089e-05</v>
       </c>
       <c r="N22">
-        <v>6.5166316608058637e-05</v>
+        <v>6.5200146862335402e-05</v>
       </c>
       <c r="O22">
-        <v>5.4496578314349765e-05</v>
+        <v>5.4530800481503681e-05</v>
       </c>
       <c r="P22">
-        <v>5.0756281960641033e-05</v>
+        <v>5.0843511466612946e-05</v>
       </c>
       <c r="Q22">
-        <v>-9.3325764638094708e-05</v>
+        <v>-9.3347218570766438e-05</v>
       </c>
       <c r="R22">
-        <v>-7.3405906387087367e-05</v>
+        <v>-7.3419817233912727e-05</v>
       </c>
       <c r="S22">
-        <v>-0.00013019832926160603</v>
+        <v>-0.00013035026285169256</v>
       </c>
       <c r="T22">
-        <v>-0.00010625516236494319</v>
+        <v>-0.0001062652756716239</v>
       </c>
       <c r="U22">
-        <v>-9.846589372160177e-05</v>
+        <v>-9.8489935979540616e-05</v>
       </c>
       <c r="V22">
-        <v>-0.00010800137532225124</v>
+        <v>-0.00010801340622833765</v>
       </c>
       <c r="W22">
-        <v>6.9904220786336561e-05</v>
+        <v>6.990424412946526e-05</v>
       </c>
       <c r="X22">
-        <v>-0.00049824852550285929</v>
+        <v>-0.00049818190918030309</v>
       </c>
       <c r="Y22">
-        <v>0.0013664630881055351</v>
+        <v>0.0013654990943034462</v>
       </c>
     </row>
     <row r="23">
@@ -2251,76 +2251,76 @@
         <v>37</v>
       </c>
       <c r="B23">
-        <v>0.20969464185683462</v>
+        <v>0.20983889692407459</v>
       </c>
       <c r="C23">
-        <v>0.00017967249437391601</v>
+        <v>0.00018073783339145636</v>
       </c>
       <c r="D23">
-        <v>0.00020807677731464469</v>
+        <v>0.00020734956898646462</v>
       </c>
       <c r="E23">
-        <v>-1.0672267744552206e-06</v>
+        <v>-1.0624288981172418e-06</v>
       </c>
       <c r="F23">
-        <v>0.00058318881328912886</v>
+        <v>0.00058315810217423464</v>
       </c>
       <c r="G23">
-        <v>0.0008560236571222013</v>
+        <v>0.0008561282207184967</v>
       </c>
       <c r="H23">
-        <v>0.00037094442234440294</v>
+        <v>0.00037086542311981865</v>
       </c>
       <c r="I23">
-        <v>6.8865382215900191e-05</v>
+        <v>6.9311461262675693e-05</v>
       </c>
       <c r="J23">
-        <v>-0.00076411163723786452</v>
+        <v>-0.0007638186510975295</v>
       </c>
       <c r="K23">
-        <v>-0.00018097421900054901</v>
+        <v>-0.00018034555545380811</v>
       </c>
       <c r="L23">
-        <v>0.00040170218584037703</v>
+        <v>0.00040281613969062177</v>
       </c>
       <c r="M23">
-        <v>0.00016975790142951044</v>
+        <v>0.00016971353593052494</v>
       </c>
       <c r="N23">
-        <v>-7.823868714326894e-05</v>
+        <v>-7.8600624646599053e-05</v>
       </c>
       <c r="O23">
-        <v>-5.4112602704414412e-05</v>
+        <v>-5.4496344426982826e-05</v>
       </c>
       <c r="P23">
-        <v>0.00013244538250348713</v>
+        <v>0.00013112722604240071</v>
       </c>
       <c r="Q23">
-        <v>0.00032880682921118329</v>
+        <v>0.00032897643488462736</v>
       </c>
       <c r="R23">
-        <v>0.00029141810043692863</v>
+        <v>0.00029153687380506239</v>
       </c>
       <c r="S23">
-        <v>0.00038933629810280601</v>
+        <v>0.00039156635859698401</v>
       </c>
       <c r="T23">
-        <v>0.00049932194704069895</v>
+        <v>0.00049934655680046892</v>
       </c>
       <c r="U23">
-        <v>0.00037416261987828752</v>
+        <v>0.00037435262496879253</v>
       </c>
       <c r="V23">
-        <v>0.00040621572446263542</v>
+        <v>0.00040624947794898119</v>
       </c>
       <c r="W23">
-        <v>-0.00049824852550285929</v>
+        <v>-0.00049818190918030309</v>
       </c>
       <c r="X23">
-        <v>0.0058725078948183148</v>
+        <v>0.005871367293781727</v>
       </c>
       <c r="Y23">
-        <v>-0.0042879551668433824</v>
+        <v>-0.0042629935029920366</v>
       </c>
     </row>
     <row r="24">
@@ -2328,76 +2328,76 @@
         <v>38</v>
       </c>
       <c r="B24">
-        <v>-0.4867131076385427</v>
+        <v>-0.48889273775295861</v>
       </c>
       <c r="C24">
-        <v>-0.016786004743844087</v>
+        <v>-0.016808861133236104</v>
       </c>
       <c r="D24">
-        <v>-0.2606092566568865</v>
+        <v>-0.26068014295401309</v>
       </c>
       <c r="E24">
-        <v>0.0020807988194184255</v>
+        <v>0.0020813413306304922</v>
       </c>
       <c r="F24">
-        <v>0.18104754929897471</v>
+        <v>0.18106981320598359</v>
       </c>
       <c r="G24">
-        <v>0.16648058498717488</v>
+        <v>0.16650170403807674</v>
       </c>
       <c r="H24">
-        <v>-0.014598934105944851</v>
+        <v>-0.014602595817448792</v>
       </c>
       <c r="I24">
-        <v>-0.028443720688763968</v>
+        <v>-0.028459061067412694</v>
       </c>
       <c r="J24">
-        <v>-0.15992006007432602</v>
+        <v>-0.15992406178289431</v>
       </c>
       <c r="K24">
-        <v>-0.0060027937355755789</v>
+        <v>-0.0060137935834939371</v>
       </c>
       <c r="L24">
-        <v>-0.016766972410609253</v>
+        <v>-0.016787752027816405</v>
       </c>
       <c r="M24">
-        <v>-0.015544252096871589</v>
+        <v>-0.015546372834418024</v>
       </c>
       <c r="N24">
-        <v>-0.024154787573449715</v>
+        <v>-0.024154563808679808</v>
       </c>
       <c r="O24">
-        <v>-0.034910163465996208</v>
+        <v>-0.034916024665207573</v>
       </c>
       <c r="P24">
-        <v>0.01484495010740073</v>
+        <v>0.014871309672353936</v>
       </c>
       <c r="Q24">
-        <v>-0.035531996191273785</v>
+        <v>-0.035544470176122403</v>
       </c>
       <c r="R24">
-        <v>-0.055972733833845739</v>
+        <v>-0.055988083672354416</v>
       </c>
       <c r="S24">
-        <v>-0.053228862965667229</v>
+        <v>-0.053277359124532006</v>
       </c>
       <c r="T24">
-        <v>-0.049229459033065845</v>
+        <v>-0.049241013287212226</v>
       </c>
       <c r="U24">
-        <v>-0.058015549226256874</v>
+        <v>-0.058030625533849134</v>
       </c>
       <c r="V24">
-        <v>-0.052227684954312625</v>
+        <v>-0.052241337165325003</v>
       </c>
       <c r="W24">
-        <v>0.0013664630881055351</v>
+        <v>0.0013654990943034462</v>
       </c>
       <c r="X24">
-        <v>-0.0042879551668433824</v>
+        <v>-0.0042629935029920366</v>
       </c>
       <c r="Y24">
-        <v>8.1937386786608073</v>
+        <v>8.1960807677630143</v>
       </c>
     </row>
   </sheetData>
@@ -2515,97 +2515,97 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>0.48725317902561055</v>
+        <v>0.46828156083912664</v>
       </c>
       <c r="C2">
-        <v>0.0014023943484551759</v>
+        <v>0.001317933254590131</v>
       </c>
       <c r="D2">
-        <v>0.00024287219891213941</v>
+        <v>0.00026351995467891723</v>
       </c>
       <c r="E2">
-        <v>-1.7429664898839259e-06</v>
+        <v>-1.8949087682106189e-06</v>
       </c>
       <c r="F2">
-        <v>0.0001376122337789315</v>
+        <v>0.00016125286979863651</v>
       </c>
       <c r="G2">
-        <v>0.00010619743153305071</v>
+        <v>0.00014019254357231393</v>
       </c>
       <c r="H2">
-        <v>5.7210452920590894e-05</v>
+        <v>5.2905596644327236e-05</v>
       </c>
       <c r="I2">
-        <v>-9.4386538690615702e-06</v>
+        <v>-1.75292618269532e-05</v>
       </c>
       <c r="J2">
-        <v>-0.00026256428078038848</v>
+        <v>-0.00022022144852791754</v>
       </c>
       <c r="K2">
-        <v>0.00065929083599635622</v>
+        <v>0.00066123127470460355</v>
       </c>
       <c r="L2">
-        <v>-3.8218426804469499e-06</v>
+        <v>-4.8913121880072967e-05</v>
       </c>
       <c r="M2">
-        <v>5.6139993627165761e-05</v>
+        <v>6.0159217809408101e-05</v>
       </c>
       <c r="N2">
-        <v>8.5235100534041805e-05</v>
+        <v>7.9045820025245081e-05</v>
       </c>
       <c r="O2">
-        <v>0.00015412556938098774</v>
+        <v>0.00011942233552537671</v>
       </c>
       <c r="P2">
-        <v>0.00012724761698980827</v>
+        <v>0.00011547551740743927</v>
       </c>
       <c r="Q2">
-        <v>-0.00041912642414828775</v>
+        <v>-0.00042326165195228981</v>
       </c>
       <c r="R2">
-        <v>0.00078794856558135076</v>
+        <v>0.00067479034677417641</v>
       </c>
       <c r="S2">
-        <v>-0.00022511761873168627</v>
+        <v>-0.00029874274436318573</v>
       </c>
       <c r="T2">
-        <v>-0.00029401555776640111</v>
+        <v>-0.00012882799477750343</v>
       </c>
       <c r="U2">
-        <v>-5.993302321163045e-05</v>
+        <v>-4.3888650747473957e-05</v>
       </c>
       <c r="V2">
-        <v>0.00012888864281596204</v>
+        <v>0.00011905073398588788</v>
       </c>
       <c r="W2">
-        <v>0.00013345126425377005</v>
+        <v>0.00012246231362551363</v>
       </c>
       <c r="X2">
-        <v>0.00013106945136016793</v>
+        <v>0.00011841634004566988</v>
       </c>
       <c r="Y2">
-        <v>7.3175256894544811e-05</v>
+        <v>5.3230216531714952e-05</v>
       </c>
       <c r="Z2">
-        <v>0.00016233783158817053</v>
+        <v>0.00013865831618414338</v>
       </c>
       <c r="AA2">
-        <v>0.00012388701297518954</v>
+        <v>0.00010818608546091598</v>
       </c>
       <c r="AB2">
-        <v>2.0847743153764003e-05</v>
+        <v>6.904116465748897e-06</v>
       </c>
       <c r="AC2">
-        <v>3.9004104743595812e-06</v>
+        <v>2.5353164022284618e-06</v>
       </c>
       <c r="AD2">
-        <v>-3.2800634213444929e-05</v>
+        <v>-2.3776572513753403e-05</v>
       </c>
       <c r="AE2">
-        <v>-1.6362622963248278e-05</v>
+        <v>-6.2605724090432444e-06</v>
       </c>
       <c r="AF2">
-        <v>-0.0098211081736195426</v>
+        <v>-0.010362830863151266</v>
       </c>
     </row>
     <row r="3">
@@ -2613,97 +2613,97 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>-0.12095583018363691</v>
+        <v>-0.13305849153237556</v>
       </c>
       <c r="C3">
-        <v>0.00024287219891213941</v>
+        <v>0.00026351995467891723</v>
       </c>
       <c r="D3">
-        <v>0.0039527956041074744</v>
+        <v>0.0039911821609429216</v>
       </c>
       <c r="E3">
-        <v>-3.2281745429263941e-05</v>
+        <v>-3.2617005872278605e-05</v>
       </c>
       <c r="F3">
-        <v>-0.0031197645712481847</v>
+        <v>-0.0030743431384759601</v>
       </c>
       <c r="G3">
-        <v>-0.0028849964840070713</v>
+        <v>-0.0028461126722139837</v>
       </c>
       <c r="H3">
-        <v>-1.2630467781720063e-05</v>
+        <v>-1.6699693319072303e-05</v>
       </c>
       <c r="I3">
-        <v>-3.4558698066657068e-05</v>
+        <v>-3.8891188909944211e-05</v>
       </c>
       <c r="J3">
-        <v>0.0029619189174806548</v>
+        <v>0.0029036669500218798</v>
       </c>
       <c r="K3">
-        <v>-0.00011510488516653424</v>
+        <v>-0.00010827520633596363</v>
       </c>
       <c r="L3">
-        <v>0.00064350311175299414</v>
+        <v>0.00062770874967373914</v>
       </c>
       <c r="M3">
-        <v>0.00010613943597936881</v>
+        <v>9.6512158729210318e-05</v>
       </c>
       <c r="N3">
-        <v>-0.00013100128436809369</v>
+        <v>-0.00013184482315622016</v>
       </c>
       <c r="O3">
-        <v>-8.7506815788145585e-05</v>
+        <v>-8.1319415389565462e-05</v>
       </c>
       <c r="P3">
-        <v>-0.00018659072133111153</v>
+        <v>-0.00018703019726721941</v>
       </c>
       <c r="Q3">
-        <v>-0.00020851444792344175</v>
+        <v>-0.00020887139217288945</v>
       </c>
       <c r="R3">
-        <v>0.0001459489014538802</v>
+        <v>0.00033549961559651859</v>
       </c>
       <c r="S3">
-        <v>-0.00027466335224897356</v>
+        <v>-0.00021927914050563421</v>
       </c>
       <c r="T3">
-        <v>-5.5695224003948773e-05</v>
+        <v>-0.00047693563485250515</v>
       </c>
       <c r="U3">
-        <v>-8.3519287051491732e-05</v>
+        <v>-8.7403088317757407e-05</v>
       </c>
       <c r="V3">
-        <v>-5.6131187514539549e-05</v>
+        <v>-3.9630962419177907e-05</v>
       </c>
       <c r="W3">
-        <v>-6.7465016128392952e-05</v>
+        <v>-5.6088664379352893e-05</v>
       </c>
       <c r="X3">
-        <v>9.7113256569275608e-06</v>
+        <v>2.3621705846563201e-05</v>
       </c>
       <c r="Y3">
-        <v>-2.7242360513751035e-05</v>
+        <v>1.2143799227627705e-06</v>
       </c>
       <c r="Z3">
-        <v>6.6150673977263819e-05</v>
+        <v>6.9302106205107461e-05</v>
       </c>
       <c r="AA3">
-        <v>7.5648819666561395e-05</v>
+        <v>9.9680704468585457e-05</v>
       </c>
       <c r="AB3">
-        <v>-2.1534158072024356e-05</v>
+        <v>-7.81267756554474e-06</v>
       </c>
       <c r="AC3">
-        <v>7.954545316162789e-06</v>
+        <v>7.9028390590845342e-06</v>
       </c>
       <c r="AD3">
-        <v>-2.3302600625496606e-05</v>
+        <v>-3.6344385382469646e-05</v>
       </c>
       <c r="AE3">
-        <v>-0.00011881164137514388</v>
+        <v>-0.00011806164469294056</v>
       </c>
       <c r="AF3">
-        <v>-0.12073367643394517</v>
+        <v>-0.12185803817751206</v>
       </c>
     </row>
     <row r="4">
@@ -2711,97 +2711,97 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>0.0024479032100635924</v>
+        <v>0.0025587336153346401</v>
       </c>
       <c r="C4">
-        <v>-1.7429664898839259e-06</v>
+        <v>-1.8949087682106189e-06</v>
       </c>
       <c r="D4">
-        <v>-3.2281745429263941e-05</v>
+        <v>-3.2617005872278605e-05</v>
       </c>
       <c r="E4">
-        <v>2.6538923691489421e-07</v>
+        <v>2.6828608101512658e-07</v>
       </c>
       <c r="F4">
-        <v>2.6923308276625025e-05</v>
+        <v>2.6529668322655101e-05</v>
       </c>
       <c r="G4">
-        <v>2.4837826352108803e-05</v>
+        <v>2.4491446781841578e-05</v>
       </c>
       <c r="H4">
-        <v>1.4152207595901491e-07</v>
+        <v>1.7343125147841508e-07</v>
       </c>
       <c r="I4">
-        <v>1.5420584067691331e-07</v>
+        <v>1.9391287751345271e-07</v>
       </c>
       <c r="J4">
-        <v>-2.6486276980159339e-05</v>
+        <v>-2.6012675408419359e-05</v>
       </c>
       <c r="K4">
-        <v>8.1217854129133488e-07</v>
+        <v>7.5152924264724531e-07</v>
       </c>
       <c r="L4">
-        <v>-5.1681576350768416e-06</v>
+        <v>-5.0196387272318454e-06</v>
       </c>
       <c r="M4">
-        <v>-9.5254960438671431e-07</v>
+        <v>-8.7456991016698362e-07</v>
       </c>
       <c r="N4">
-        <v>9.8398391760685445e-07</v>
+        <v>9.9457475663084313e-07</v>
       </c>
       <c r="O4">
-        <v>6.4323715881421417e-07</v>
+        <v>6.0846141394254764e-07</v>
       </c>
       <c r="P4">
-        <v>1.4353804087846752e-06</v>
+        <v>1.4432278013997932e-06</v>
       </c>
       <c r="Q4">
-        <v>1.8037157605078595e-06</v>
+        <v>1.8094565872085687e-06</v>
       </c>
       <c r="R4">
-        <v>-1.4848012337321137e-06</v>
+        <v>-3.0130221747405795e-06</v>
       </c>
       <c r="S4">
-        <v>2.2750375750720358e-06</v>
+        <v>1.6623732069506259e-06</v>
       </c>
       <c r="T4">
-        <v>3.0226665811251352e-07</v>
+        <v>3.984075981260774e-06</v>
       </c>
       <c r="U4">
-        <v>6.0524281928056372e-07</v>
+        <v>6.3141847957079455e-07</v>
       </c>
       <c r="V4">
-        <v>4.9716219899972034e-07</v>
+        <v>3.6666186084683935e-07</v>
       </c>
       <c r="W4">
-        <v>6.662090024405409e-07</v>
+        <v>5.8161907022155884e-07</v>
       </c>
       <c r="X4">
-        <v>1.38548718467261e-07</v>
+        <v>3.2856827072145524e-08</v>
       </c>
       <c r="Y4">
-        <v>2.4592369572416545e-07</v>
+        <v>2.6728374349146034e-08</v>
       </c>
       <c r="Z4">
-        <v>-3.6777087458663565e-07</v>
+        <v>-3.7698988840557685e-07</v>
       </c>
       <c r="AA4">
-        <v>-4.9821489612415087e-07</v>
+        <v>-6.8591618313773562e-07</v>
       </c>
       <c r="AB4">
-        <v>1.7642125534409045e-07</v>
+        <v>7.4841568163490618e-08</v>
       </c>
       <c r="AC4">
-        <v>-8.8276431555639443e-08</v>
+        <v>-8.6962150874775284e-08</v>
       </c>
       <c r="AD4">
-        <v>8.8175852370998235e-08</v>
+        <v>1.9120497312020849e-07</v>
       </c>
       <c r="AE4">
-        <v>8.6192674716333495e-07</v>
+        <v>8.4897259201063401e-07</v>
       </c>
       <c r="AF4">
-        <v>0.00098004909252421158</v>
+        <v>0.0009899097002269196</v>
       </c>
     </row>
     <row r="5">
@@ -2809,97 +2809,97 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>1.387842281524813</v>
+        <v>1.3694363247794523</v>
       </c>
       <c r="C5">
-        <v>0.0001376122337789315</v>
+        <v>0.00016125286979863651</v>
       </c>
       <c r="D5">
-        <v>-0.0031197645712481847</v>
+        <v>-0.0030743431384759601</v>
       </c>
       <c r="E5">
-        <v>2.6923308276625025e-05</v>
+        <v>2.6529668322655101e-05</v>
       </c>
       <c r="F5">
-        <v>0.0065662181812897007</v>
+        <v>0.0066015099205308618</v>
       </c>
       <c r="G5">
-        <v>0.0044284622041411772</v>
+        <v>0.0044686807341489318</v>
       </c>
       <c r="H5">
-        <v>3.6955261712149322e-05</v>
+        <v>3.0361065631737474e-05</v>
       </c>
       <c r="I5">
-        <v>-8.1903891452066169e-05</v>
+        <v>-9.1843111118318846e-05</v>
       </c>
       <c r="J5">
-        <v>-0.0061118219882119601</v>
+        <v>-0.0061390699349622921</v>
       </c>
       <c r="K5">
-        <v>3.9441223486048546e-05</v>
+        <v>3.9967890983191867e-05</v>
       </c>
       <c r="L5">
-        <v>0.00028054979351586559</v>
+        <v>0.00023842254359761166</v>
       </c>
       <c r="M5">
-        <v>-0.00015832672271775226</v>
+        <v>-0.00016210494769831538</v>
       </c>
       <c r="N5">
-        <v>-6.0067415039244745e-06</v>
+        <v>-1.0757101683266102e-05</v>
       </c>
       <c r="O5">
-        <v>-2.0086948044259305e-05</v>
+        <v>-2.5411319357183417e-05</v>
       </c>
       <c r="P5">
-        <v>0.00013679014965022485</v>
+        <v>0.00012613560276452523</v>
       </c>
       <c r="Q5">
-        <v>0.00017392951375968559</v>
+        <v>0.00017638354082061833</v>
       </c>
       <c r="R5">
-        <v>0.00035359481747339761</v>
+        <v>0.0005334614974869048</v>
       </c>
       <c r="S5">
-        <v>-0.00050320506515459662</v>
+        <v>-0.0010446205190958319</v>
       </c>
       <c r="T5">
-        <v>-0.00093313740148424571</v>
+        <v>-0.00051706008620285709</v>
       </c>
       <c r="U5">
-        <v>1.3152189557902143e-05</v>
+        <v>2.754369199701838e-06</v>
       </c>
       <c r="V5">
-        <v>6.306579232923798e-05</v>
+        <v>7.7288522244261734e-05</v>
       </c>
       <c r="W5">
-        <v>0.00014470626196641523</v>
+        <v>0.00015317646621142156</v>
       </c>
       <c r="X5">
-        <v>0.0001435653601878778</v>
+        <v>0.00014883785957289786</v>
       </c>
       <c r="Y5">
-        <v>4.6333843239345501e-05</v>
+        <v>6.0600137503937987e-05</v>
       </c>
       <c r="Z5">
-        <v>9.461183932895495e-05</v>
+        <v>0.0001030180871239017</v>
       </c>
       <c r="AA5">
-        <v>-1.5450365248449727e-05</v>
+        <v>-2.615179518489566e-06</v>
       </c>
       <c r="AB5">
-        <v>2.2784830465763517e-05</v>
+        <v>2.8694224247772376e-05</v>
       </c>
       <c r="AC5">
-        <v>-2.562358652305935e-05</v>
+        <v>-2.65208927625434e-05</v>
       </c>
       <c r="AD5">
-        <v>1.9954943073725862e-05</v>
+        <v>1.2217974530180642e-05</v>
       </c>
       <c r="AE5">
-        <v>4.1295043706562895e-05</v>
+        <v>4.8669687654673971e-05</v>
       </c>
       <c r="AF5">
-        <v>0.090213049877748031</v>
+        <v>0.08891250148184171</v>
       </c>
     </row>
     <row r="6">
@@ -2907,97 +2907,97 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>1.1109799283611093</v>
+        <v>1.1027322902605532</v>
       </c>
       <c r="C6">
-        <v>0.00010619743153305071</v>
+        <v>0.00014019254357231393</v>
       </c>
       <c r="D6">
-        <v>-0.0028849964840070713</v>
+        <v>-0.0028461126722139837</v>
       </c>
       <c r="E6">
-        <v>2.4837826352108803e-05</v>
+        <v>2.4491446781841578e-05</v>
       </c>
       <c r="F6">
-        <v>0.0044284622041411772</v>
+        <v>0.0044686807341489318</v>
       </c>
       <c r="G6">
-        <v>0.0072061004302717072</v>
+        <v>0.0072606191181155584</v>
       </c>
       <c r="H6">
-        <v>-2.4395485181322716e-05</v>
+        <v>-2.8816378452953847e-05</v>
       </c>
       <c r="I6">
-        <v>-6.8580656132906197e-05</v>
+        <v>-7.6316453111400715e-05</v>
       </c>
       <c r="J6">
-        <v>-0.0053275577779112945</v>
+        <v>-0.0053722389513483695</v>
       </c>
       <c r="K6">
-        <v>3.0970564203409642e-05</v>
+        <v>3.3980678954891735e-05</v>
       </c>
       <c r="L6">
-        <v>2.3004361085097666e-05</v>
+        <v>1.0631622524553269e-06</v>
       </c>
       <c r="M6">
-        <v>-9.238939590995067e-05</v>
+        <v>-8.7598100233475529e-05</v>
       </c>
       <c r="N6">
-        <v>6.8097054835612649e-05</v>
+        <v>6.6364127081302259e-05</v>
       </c>
       <c r="O6">
-        <v>2.4205367652443879e-05</v>
+        <v>2.8065530651967974e-05</v>
       </c>
       <c r="P6">
-        <v>0.00015193521622598218</v>
+        <v>0.00015498686885990869</v>
       </c>
       <c r="Q6">
-        <v>0.00016886192199491246</v>
+        <v>0.00017383092497874272</v>
       </c>
       <c r="R6">
-        <v>0.00019957995172552832</v>
+        <v>0.00039766183659994004</v>
       </c>
       <c r="S6">
-        <v>-0.00041744464422944529</v>
+        <v>-0.0009321461225941137</v>
       </c>
       <c r="T6">
-        <v>-0.00080820040715199812</v>
+        <v>-0.0005128743988593509</v>
       </c>
       <c r="U6">
-        <v>4.906263521241034e-05</v>
+        <v>3.5950533332993959e-05</v>
       </c>
       <c r="V6">
-        <v>0.00010101082290138452</v>
+        <v>0.00011735735905567344</v>
       </c>
       <c r="W6">
-        <v>5.7965831031604742e-05</v>
+        <v>5.5624645884946866e-05</v>
       </c>
       <c r="X6">
-        <v>-2.5862671698198558e-06</v>
+        <v>-6.1543642715794489e-06</v>
       </c>
       <c r="Y6">
-        <v>-4.3240048640454457e-05</v>
+        <v>-4.5158532275312371e-05</v>
       </c>
       <c r="Z6">
-        <v>-5.6786065210284731e-05</v>
+        <v>-5.2784243551179388e-05</v>
       </c>
       <c r="AA6">
-        <v>-0.00015583452042863821</v>
+        <v>-0.00015847080904152558</v>
       </c>
       <c r="AB6">
-        <v>-5.9981935310825935e-05</v>
+        <v>-6.1231019737612719e-05</v>
       </c>
       <c r="AC6">
-        <v>-2.1539599776004468e-05</v>
+        <v>-2.1592680214786318e-05</v>
       </c>
       <c r="AD6">
-        <v>-5.2777360766777942e-05</v>
+        <v>-5.6279052144281305e-05</v>
       </c>
       <c r="AE6">
-        <v>4.4807082904333578e-05</v>
+        <v>4.852695168872101e-05</v>
       </c>
       <c r="AF6">
-        <v>0.083696769059056486</v>
+        <v>0.082591000956276639</v>
       </c>
     </row>
     <row r="7">
@@ -3005,97 +3005,97 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <v>0.040707480896544523</v>
+        <v>0.03905795925593878</v>
       </c>
       <c r="C7">
-        <v>5.7210452920590894e-05</v>
+        <v>5.2905596644327236e-05</v>
       </c>
       <c r="D7">
-        <v>-1.2630467781720063e-05</v>
+        <v>-1.6699693319072303e-05</v>
       </c>
       <c r="E7">
-        <v>1.4152207595901491e-07</v>
+        <v>1.7343125147841508e-07</v>
       </c>
       <c r="F7">
-        <v>3.6955261712149322e-05</v>
+        <v>3.0361065631737474e-05</v>
       </c>
       <c r="G7">
-        <v>-2.4395485181322716e-05</v>
+        <v>-2.8816378452953847e-05</v>
       </c>
       <c r="H7">
-        <v>0.0018008350324867231</v>
+        <v>0.0018053396591577989</v>
       </c>
       <c r="I7">
-        <v>0.0010046658368847616</v>
+        <v>0.0010075705447430221</v>
       </c>
       <c r="J7">
-        <v>6.4020646173056171e-05</v>
+        <v>7.096464307682418e-05</v>
       </c>
       <c r="K7">
-        <v>-9.276549605458094e-05</v>
+        <v>-9.5817491673552506e-05</v>
       </c>
       <c r="L7">
-        <v>-7.6583277711712481e-05</v>
+        <v>-7.6062093547468929e-05</v>
       </c>
       <c r="M7">
-        <v>-6.3015617022360538e-06</v>
+        <v>-5.3617857572944134e-06</v>
       </c>
       <c r="N7">
-        <v>-1.9504066919595633e-05</v>
+        <v>-2.4116853083533811e-05</v>
       </c>
       <c r="O7">
-        <v>-3.8522040883761852e-05</v>
+        <v>-4.6698585106363228e-05</v>
       </c>
       <c r="P7">
-        <v>0.00034026502123803213</v>
+        <v>0.00033649144332574543</v>
       </c>
       <c r="Q7">
-        <v>5.6725075104128005e-05</v>
+        <v>5.6744577319602142e-05</v>
       </c>
       <c r="R7">
-        <v>4.3471605720680405e-05</v>
+        <v>2.7001880979072185e-05</v>
       </c>
       <c r="S7">
-        <v>-2.2661785328908856e-05</v>
+        <v>-3.5516595288080091e-05</v>
       </c>
       <c r="T7">
-        <v>-5.7469043889428104e-05</v>
+        <v>3.8815558325247458e-05</v>
       </c>
       <c r="U7">
-        <v>-1.4416054766716179e-05</v>
+        <v>-1.5690043718079186e-05</v>
       </c>
       <c r="V7">
-        <v>5.7839320015892922e-05</v>
+        <v>5.4984855633013877e-05</v>
       </c>
       <c r="W7">
-        <v>8.9744080367285635e-05</v>
+        <v>8.4693385359520821e-05</v>
       </c>
       <c r="X7">
-        <v>0.00010561664733128601</v>
+        <v>0.00010227449040021161</v>
       </c>
       <c r="Y7">
-        <v>0.0001253563055107607</v>
+        <v>0.00012191385129444571</v>
       </c>
       <c r="Z7">
-        <v>0.00014931859647228504</v>
+        <v>0.00014436710684840757</v>
       </c>
       <c r="AA7">
-        <v>9.1864724172606199e-05</v>
+        <v>8.7246765201815511e-05</v>
       </c>
       <c r="AB7">
-        <v>0.00012677015335271161</v>
+        <v>0.0001216628739850352</v>
       </c>
       <c r="AC7">
-        <v>-1.2375192441873928e-07</v>
+        <v>-7.5258779324508928e-08</v>
       </c>
       <c r="AD7">
-        <v>6.6943520880069843e-06</v>
+        <v>5.0381547394161199e-06</v>
       </c>
       <c r="AE7">
-        <v>-7.5394154640962691e-06</v>
+        <v>-8.4157082835525834e-06</v>
       </c>
       <c r="AF7">
-        <v>-0.00088888510185315337</v>
+        <v>-0.00074842086026358917</v>
       </c>
     </row>
     <row r="8">
@@ -3103,97 +3103,97 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>-0.014699788925427861</v>
+        <v>-0.015066034547928358</v>
       </c>
       <c r="C8">
-        <v>-9.4386538690615702e-06</v>
+        <v>-1.75292618269532e-05</v>
       </c>
       <c r="D8">
-        <v>-3.4558698066657068e-05</v>
+        <v>-3.8891188909944211e-05</v>
       </c>
       <c r="E8">
-        <v>1.5420584067691331e-07</v>
+        <v>1.9391287751345271e-07</v>
       </c>
       <c r="F8">
-        <v>-8.1903891452066169e-05</v>
+        <v>-9.1843111118318846e-05</v>
       </c>
       <c r="G8">
-        <v>-6.8580656132906197e-05</v>
+        <v>-7.6316453111400715e-05</v>
       </c>
       <c r="H8">
-        <v>0.0010046658368847616</v>
+        <v>0.0010075705447430221</v>
       </c>
       <c r="I8">
-        <v>0.0014502975289868681</v>
+        <v>0.0014538949950025457</v>
       </c>
       <c r="J8">
-        <v>0.00016133381018938503</v>
+        <v>0.00017104066956493162</v>
       </c>
       <c r="K8">
-        <v>-0.0001436979955878347</v>
+        <v>-0.00014644758320911014</v>
       </c>
       <c r="L8">
-        <v>-3.1695056225983492e-05</v>
+        <v>-2.7988680859991437e-05</v>
       </c>
       <c r="M8">
-        <v>3.4720913991057934e-05</v>
+        <v>3.6893921217557126e-05</v>
       </c>
       <c r="N8">
-        <v>8.4960994955118592e-05</v>
+        <v>8.2605719810949547e-05</v>
       </c>
       <c r="O8">
-        <v>0.00013391735913121093</v>
+        <v>0.00012999567124037076</v>
       </c>
       <c r="P8">
-        <v>0.00056354778732926631</v>
+        <v>0.00056161171625847804</v>
       </c>
       <c r="Q8">
-        <v>1.3093487704130687e-05</v>
+        <v>1.3745747940808854e-05</v>
       </c>
       <c r="R8">
-        <v>-1.3775472791114062e-05</v>
+        <v>-5.0477405441336413e-05</v>
       </c>
       <c r="S8">
-        <v>6.6612424270576779e-05</v>
+        <v>0.00011539642106720392</v>
       </c>
       <c r="T8">
-        <v>7.8908114838060215e-05</v>
+        <v>6.8919768821180149e-05</v>
       </c>
       <c r="U8">
-        <v>1.5554265670880837e-06</v>
+        <v>3.1646010236562169e-06</v>
       </c>
       <c r="V8">
-        <v>-1.5639148942113326e-06</v>
+        <v>-3.3708711019775415e-06</v>
       </c>
       <c r="W8">
-        <v>-0.0001511264226981817</v>
+        <v>-0.00015199253212248224</v>
       </c>
       <c r="X8">
-        <v>-0.00011572734246231332</v>
+        <v>-0.00011537836761782016</v>
       </c>
       <c r="Y8">
-        <v>2.1116077383386407e-05</v>
+        <v>2.1642693637046503e-05</v>
       </c>
       <c r="Z8">
-        <v>-0.00014420484570888768</v>
+        <v>-0.00014584323727857406</v>
       </c>
       <c r="AA8">
-        <v>-0.00011077226515824007</v>
+        <v>-0.00011108130216969212</v>
       </c>
       <c r="AB8">
-        <v>-0.00011622786640813599</v>
+        <v>-0.0001170967151515451</v>
       </c>
       <c r="AC8">
-        <v>1.9269307085190652e-05</v>
+        <v>1.9389961749731991e-05</v>
       </c>
       <c r="AD8">
-        <v>-8.1355723930311825e-06</v>
+        <v>-8.5274694678563897e-06</v>
       </c>
       <c r="AE8">
-        <v>7.5426767904021802e-06</v>
+        <v>6.5353898931124832e-06</v>
       </c>
       <c r="AF8">
-        <v>0.00011886449373839716</v>
+        <v>0.00024179104459880023</v>
       </c>
     </row>
     <row r="9">
@@ -3201,97 +3201,97 @@
         <v>23</v>
       </c>
       <c r="B9">
-        <v>-0.5234979315511783</v>
+        <v>-0.50468778583287344</v>
       </c>
       <c r="C9">
-        <v>-0.00026256428078038848</v>
+        <v>-0.00022022144852791754</v>
       </c>
       <c r="D9">
-        <v>0.0029619189174806548</v>
+        <v>0.0029036669500218798</v>
       </c>
       <c r="E9">
-        <v>-2.6486276980159339e-05</v>
+        <v>-2.6012675408419359e-05</v>
       </c>
       <c r="F9">
-        <v>-0.0061118219882119601</v>
+        <v>-0.0061390699349622921</v>
       </c>
       <c r="G9">
-        <v>-0.0053275577779112945</v>
+        <v>-0.0053722389513483695</v>
       </c>
       <c r="H9">
-        <v>6.4020646173056171e-05</v>
+        <v>7.096464307682418e-05</v>
       </c>
       <c r="I9">
-        <v>0.00016133381018938503</v>
+        <v>0.00017104066956493162</v>
       </c>
       <c r="J9">
-        <v>0.0094636796867248948</v>
+        <v>0.0094388770424811905</v>
       </c>
       <c r="K9">
-        <v>0.00055999224830077972</v>
+        <v>0.00055569331545706272</v>
       </c>
       <c r="L9">
-        <v>-0.0025689893281114311</v>
+        <v>-0.0025102359203569794</v>
       </c>
       <c r="M9">
-        <v>0.00017090657125657348</v>
+        <v>0.00016607121125292862</v>
       </c>
       <c r="N9">
-        <v>-7.8841990849270322e-05</v>
+        <v>-7.3395784211771013e-05</v>
       </c>
       <c r="O9">
-        <v>-8.8772564008486165e-05</v>
+        <v>-7.098638285532935e-05</v>
       </c>
       <c r="P9">
-        <v>-0.0002435896369688776</v>
+        <v>-0.00023381371213415658</v>
       </c>
       <c r="Q9">
-        <v>-0.00036335595410660546</v>
+        <v>-0.00036123510642958163</v>
       </c>
       <c r="R9">
-        <v>-0.00069186153377019926</v>
+        <v>-0.00071843000749185126</v>
       </c>
       <c r="S9">
-        <v>0.0003826454553538328</v>
+        <v>0.00076959633285667885</v>
       </c>
       <c r="T9">
-        <v>0.00071909823055051753</v>
+        <v>0.00046056870370207292</v>
       </c>
       <c r="U9">
-        <v>-8.5727475420305406e-05</v>
+        <v>-9.9701994357434716e-05</v>
       </c>
       <c r="V9">
-        <v>-0.00018228392450622168</v>
+        <v>-0.00018217420460480294</v>
       </c>
       <c r="W9">
-        <v>-0.00016425174750533955</v>
+        <v>-0.00016400049026041308</v>
       </c>
       <c r="X9">
-        <v>-0.00015029601914325758</v>
+        <v>-0.00014747596137238556</v>
       </c>
       <c r="Y9">
-        <v>-3.0435953866161936e-05</v>
+        <v>-2.8842142467410542e-05</v>
       </c>
       <c r="Z9">
-        <v>-0.00014479438038654535</v>
+        <v>-0.00014158238213639318</v>
       </c>
       <c r="AA9">
-        <v>3.6914701583406692e-05</v>
+        <v>3.8227683195932172e-05</v>
       </c>
       <c r="AB9">
-        <v>1.8256000519498855e-05</v>
+        <v>2.333301139561747e-05</v>
       </c>
       <c r="AC9">
-        <v>3.0587791750546361e-05</v>
+        <v>3.1534090340889229e-05</v>
       </c>
       <c r="AD9">
-        <v>0.00012025088819238305</v>
+        <v>0.00012208290770163513</v>
       </c>
       <c r="AE9">
-        <v>1.539995397804167e-05</v>
+        <v>8.8173611989782186e-06</v>
       </c>
       <c r="AF9">
-        <v>-0.0826777603667746</v>
+        <v>-0.080972410481051138</v>
       </c>
     </row>
     <row r="10">
@@ -3299,97 +3299,97 @@
         <v>24</v>
       </c>
       <c r="B10">
-        <v>0.28054411507663746</v>
+        <v>0.27838996416079476</v>
       </c>
       <c r="C10">
-        <v>0.00065929083599635622</v>
+        <v>0.00066123127470460355</v>
       </c>
       <c r="D10">
-        <v>-0.00011510488516653424</v>
+        <v>-0.00010827520633596363</v>
       </c>
       <c r="E10">
-        <v>8.1217854129133488e-07</v>
+        <v>7.5152924264724531e-07</v>
       </c>
       <c r="F10">
-        <v>3.9441223486048546e-05</v>
+        <v>3.9967890983191867e-05</v>
       </c>
       <c r="G10">
-        <v>3.0970564203409642e-05</v>
+        <v>3.3980678954891735e-05</v>
       </c>
       <c r="H10">
-        <v>-9.276549605458094e-05</v>
+        <v>-9.5817491673552506e-05</v>
       </c>
       <c r="I10">
-        <v>-0.0001436979955878347</v>
+        <v>-0.00014644758320911014</v>
       </c>
       <c r="J10">
-        <v>0.00055999224830077972</v>
+        <v>0.00055569331545706272</v>
       </c>
       <c r="K10">
-        <v>0.0021866069913197041</v>
+        <v>0.0021791906095711203</v>
       </c>
       <c r="L10">
-        <v>-0.00092992344661315361</v>
+        <v>-0.00093390791806195837</v>
       </c>
       <c r="M10">
-        <v>9.3795448318696653e-05</v>
+        <v>9.2049353282732467e-05</v>
       </c>
       <c r="N10">
-        <v>0.00070180692480375617</v>
+        <v>0.00070151635845918021</v>
       </c>
       <c r="O10">
-        <v>0.0013192664166903128</v>
+        <v>0.0013125258090180498</v>
       </c>
       <c r="P10">
-        <v>0.0013209334027606951</v>
+        <v>0.0013115516340900695</v>
       </c>
       <c r="Q10">
-        <v>-0.00079499645727432059</v>
+        <v>-0.00079344262078678396</v>
       </c>
       <c r="R10">
-        <v>0.0001345809428470013</v>
+        <v>0.00016357534692175877</v>
       </c>
       <c r="S10">
-        <v>-0.0001553246597402212</v>
+        <v>-0.00031190163130372849</v>
       </c>
       <c r="T10">
-        <v>-0.00029534533075805758</v>
+        <v>-8.7108686529680239e-05</v>
       </c>
       <c r="U10">
-        <v>0.00035870791963787355</v>
+        <v>0.00035376683292267808</v>
       </c>
       <c r="V10">
-        <v>-5.0795873741489768e-05</v>
+        <v>-4.6484309492659213e-05</v>
       </c>
       <c r="W10">
-        <v>-0.00021145918025485661</v>
+        <v>-0.00020626614274486159</v>
       </c>
       <c r="X10">
-        <v>-0.00029710069986508885</v>
+        <v>-0.00029102294568792721</v>
       </c>
       <c r="Y10">
-        <v>-0.00027210251978592104</v>
+        <v>-0.00026567098142122941</v>
       </c>
       <c r="Z10">
-        <v>-0.00025539691257208904</v>
+        <v>-0.00025171508452830624</v>
       </c>
       <c r="AA10">
-        <v>-0.00020067173771618776</v>
+        <v>-0.0001951670658954595</v>
       </c>
       <c r="AB10">
-        <v>-0.00035836503714540766</v>
+        <v>-0.00035260073014265619</v>
       </c>
       <c r="AC10">
-        <v>1.0989811566303209e-05</v>
+        <v>1.0821262241786595e-05</v>
       </c>
       <c r="AD10">
-        <v>3.6627567156484659e-05</v>
+        <v>3.6093097805065867e-05</v>
       </c>
       <c r="AE10">
-        <v>3.6191158535631e-05</v>
+        <v>3.9237592265942796e-05</v>
       </c>
       <c r="AF10">
-        <v>0.0017422100399287297</v>
+        <v>0.0015604631246996618</v>
       </c>
     </row>
     <row r="11">
@@ -3397,97 +3397,97 @@
         <v>45</v>
       </c>
       <c r="B11">
-        <v>-0.74116406068219265</v>
+        <v>-0.73159263351476467</v>
       </c>
       <c r="C11">
-        <v>-3.8218426804469499e-06</v>
+        <v>-4.8913121880072967e-05</v>
       </c>
       <c r="D11">
-        <v>0.00064350311175299414</v>
+        <v>0.00062770874967373914</v>
       </c>
       <c r="E11">
-        <v>-5.1681576350768416e-06</v>
+        <v>-5.0196387272318454e-06</v>
       </c>
       <c r="F11">
-        <v>0.00028054979351586559</v>
+        <v>0.00023842254359761166</v>
       </c>
       <c r="G11">
-        <v>2.3004361085097666e-05</v>
+        <v>1.0631622524553269e-06</v>
       </c>
       <c r="H11">
-        <v>-7.6583277711712481e-05</v>
+        <v>-7.6062093547468929e-05</v>
       </c>
       <c r="I11">
-        <v>-3.1695056225983492e-05</v>
+        <v>-2.7988680859991437e-05</v>
       </c>
       <c r="J11">
-        <v>-0.0025689893281114311</v>
+        <v>-0.0025102359203569794</v>
       </c>
       <c r="K11">
-        <v>-0.00092992344661315361</v>
+        <v>-0.00093390791806195837</v>
       </c>
       <c r="L11">
-        <v>0.0041250207998630786</v>
+        <v>0.0041356211281798772</v>
       </c>
       <c r="M11">
-        <v>1.0023846696788699e-06</v>
+        <v>3.6232436102933037e-06</v>
       </c>
       <c r="N11">
-        <v>0.00012165066031736508</v>
+        <v>0.00011971662893532989</v>
       </c>
       <c r="O11">
-        <v>0.00016064099398632812</v>
+        <v>0.00015056530182096511</v>
       </c>
       <c r="P11">
-        <v>0.0002517259728055572</v>
+        <v>0.00024873667104816739</v>
       </c>
       <c r="Q11">
-        <v>0.00020502767681666902</v>
+        <v>0.00020245654437918447</v>
       </c>
       <c r="R11">
-        <v>-0.00024242249362033922</v>
+        <v>-0.00042244178030889353</v>
       </c>
       <c r="S11">
-        <v>0.00053434800485357092</v>
+        <v>0.00081219011060027499</v>
       </c>
       <c r="T11">
-        <v>0.00069419497770139551</v>
+        <v>0.00033389148418677141</v>
       </c>
       <c r="U11">
-        <v>0.00013409338565726183</v>
+        <v>0.00015073419211822446</v>
       </c>
       <c r="V11">
-        <v>9.8889032875812541e-05</v>
+        <v>9.0337666218841175e-05</v>
       </c>
       <c r="W11">
-        <v>7.9520853194377586e-05</v>
+        <v>6.7893106911379349e-05</v>
       </c>
       <c r="X11">
-        <v>2.2787685722563608e-05</v>
+        <v>9.1786741238915684e-06</v>
       </c>
       <c r="Y11">
-        <v>-7.1815127635796276e-06</v>
+        <v>-2.4033414581407526e-05</v>
       </c>
       <c r="Z11">
-        <v>4.0926054849702194e-05</v>
+        <v>3.1942064179653861e-05</v>
       </c>
       <c r="AA11">
-        <v>3.855480742998409e-05</v>
+        <v>2.1387047368748562e-05</v>
       </c>
       <c r="AB11">
-        <v>0.00017665281624254948</v>
+        <v>0.00016773148791221059</v>
       </c>
       <c r="AC11">
-        <v>1.2996587300830454e-05</v>
+        <v>1.338068976918949e-05</v>
       </c>
       <c r="AD11">
-        <v>-4.2586947257999309e-05</v>
+        <v>-4.2790836759010187e-05</v>
       </c>
       <c r="AE11">
-        <v>-5.668123728520217e-05</v>
+        <v>-6.2428390317280889e-05</v>
       </c>
       <c r="AF11">
-        <v>-0.020037704559520836</v>
+        <v>-0.019576070744094704</v>
       </c>
     </row>
     <row r="12">
@@ -3495,97 +3495,97 @@
         <v>25</v>
       </c>
       <c r="B12">
-        <v>0.045733394426548328</v>
+        <v>0.045004152394663558</v>
       </c>
       <c r="C12">
-        <v>5.6139993627165761e-05</v>
+        <v>6.0159217809408101e-05</v>
       </c>
       <c r="D12">
-        <v>0.00010613943597936881</v>
+        <v>9.6512158729210318e-05</v>
       </c>
       <c r="E12">
-        <v>-9.5254960438671431e-07</v>
+        <v>-8.7456991016698362e-07</v>
       </c>
       <c r="F12">
-        <v>-0.00015832672271775226</v>
+        <v>-0.00016210494769831538</v>
       </c>
       <c r="G12">
-        <v>-9.238939590995067e-05</v>
+        <v>-8.7598100233475529e-05</v>
       </c>
       <c r="H12">
-        <v>-6.3015617022360538e-06</v>
+        <v>-5.3617857572944134e-06</v>
       </c>
       <c r="I12">
-        <v>3.4720913991057934e-05</v>
+        <v>3.6893921217557126e-05</v>
       </c>
       <c r="J12">
-        <v>0.00017090657125657348</v>
+        <v>0.00016607121125292862</v>
       </c>
       <c r="K12">
-        <v>9.3795448318696653e-05</v>
+        <v>9.2049353282732467e-05</v>
       </c>
       <c r="L12">
-        <v>1.0023846696788699e-06</v>
+        <v>3.6232436102933037e-06</v>
       </c>
       <c r="M12">
-        <v>0.0016573290140312461</v>
+        <v>0.0016622718457168252</v>
       </c>
       <c r="N12">
-        <v>0.00082248691414557563</v>
+        <v>0.00082511256477257931</v>
       </c>
       <c r="O12">
-        <v>0.00084515597956036641</v>
+        <v>0.0008475390906643827</v>
       </c>
       <c r="P12">
-        <v>0.00085879000544015235</v>
+        <v>0.00086181643411142026</v>
       </c>
       <c r="Q12">
-        <v>-2.8053886209039567e-05</v>
+        <v>-2.4454183319798611e-05</v>
       </c>
       <c r="R12">
-        <v>-4.5460339183357929e-05</v>
+        <v>-4.6234290833055967e-05</v>
       </c>
       <c r="S12">
-        <v>5.3963192933774505e-06</v>
+        <v>7.1503245069130675e-05</v>
       </c>
       <c r="T12">
-        <v>6.2339736771488885e-05</v>
+        <v>4.7584987379977188e-05</v>
       </c>
       <c r="U12">
-        <v>5.9191160134951845e-05</v>
+        <v>5.6004843837205204e-05</v>
       </c>
       <c r="V12">
-        <v>7.8117580987995206e-05</v>
+        <v>7.7953104558420858e-05</v>
       </c>
       <c r="W12">
-        <v>-0.00014858500685012086</v>
+        <v>-0.00014442909588583091</v>
       </c>
       <c r="X12">
-        <v>-0.000102968327912793</v>
+        <v>-0.00010044767566196326</v>
       </c>
       <c r="Y12">
-        <v>-0.00013065368451483641</v>
+        <v>-0.00012464882319047032</v>
       </c>
       <c r="Z12">
-        <v>-9.2374662380601642e-05</v>
+        <v>-9.1092954269858745e-05</v>
       </c>
       <c r="AA12">
-        <v>-0.00013977880512156812</v>
+        <v>-0.00013600591306319029</v>
       </c>
       <c r="AB12">
-        <v>-4.0230297744125077e-05</v>
+        <v>-3.7767557070671242e-05</v>
       </c>
       <c r="AC12">
-        <v>1.0302928446353325e-05</v>
+        <v>1.0084306560428356e-05</v>
       </c>
       <c r="AD12">
-        <v>-6.366220707879457e-05</v>
+        <v>-6.3177250266289336e-05</v>
       </c>
       <c r="AE12">
-        <v>-1.2898703690403159e-05</v>
+        <v>-1.0207168516141178e-05</v>
       </c>
       <c r="AF12">
-        <v>-0.0039375238607508162</v>
+        <v>-0.0036488735544846183</v>
       </c>
     </row>
     <row r="13">
@@ -3593,97 +3593,97 @@
         <v>26</v>
       </c>
       <c r="B13">
-        <v>0.068725675613250797</v>
+        <v>0.066195445378885109</v>
       </c>
       <c r="C13">
-        <v>8.5235100534041805e-05</v>
+        <v>7.9045820025245081e-05</v>
       </c>
       <c r="D13">
-        <v>-0.00013100128436809369</v>
+        <v>-0.00013184482315622016</v>
       </c>
       <c r="E13">
-        <v>9.8398391760685445e-07</v>
+        <v>9.9457475663084313e-07</v>
       </c>
       <c r="F13">
-        <v>-6.0067415039244745e-06</v>
+        <v>-1.0757101683266102e-05</v>
       </c>
       <c r="G13">
-        <v>6.8097054835612649e-05</v>
+        <v>6.6364127081302259e-05</v>
       </c>
       <c r="H13">
-        <v>-1.9504066919595633e-05</v>
+        <v>-2.4116853083533811e-05</v>
       </c>
       <c r="I13">
-        <v>8.4960994955118592e-05</v>
+        <v>8.2605719810949547e-05</v>
       </c>
       <c r="J13">
-        <v>-7.8841990849270322e-05</v>
+        <v>-7.3395784211771013e-05</v>
       </c>
       <c r="K13">
-        <v>0.00070180692480375617</v>
+        <v>0.00070151635845918021</v>
       </c>
       <c r="L13">
-        <v>0.00012165066031736508</v>
+        <v>0.00011971662893532989</v>
       </c>
       <c r="M13">
-        <v>0.00082248691414557563</v>
+        <v>0.00082511256477257931</v>
       </c>
       <c r="N13">
-        <v>0.0019352751438251076</v>
+        <v>0.0019377806896897719</v>
       </c>
       <c r="O13">
-        <v>0.0015874126387094712</v>
+        <v>0.0015878241110124573</v>
       </c>
       <c r="P13">
-        <v>0.0016975543070582313</v>
+        <v>0.0016971493001531265</v>
       </c>
       <c r="Q13">
-        <v>-9.4906574066254984e-05</v>
+        <v>-9.2968393790273808e-05</v>
       </c>
       <c r="R13">
-        <v>-5.5509477907005772e-06</v>
+        <v>-2.4854932899001718e-05</v>
       </c>
       <c r="S13">
-        <v>5.019249659759422e-05</v>
+        <v>-2.2702103437804316e-05</v>
       </c>
       <c r="T13">
-        <v>-4.2348101070800487e-05</v>
+        <v>2.1865485366483043e-05</v>
       </c>
       <c r="U13">
-        <v>0.00044926220063263363</v>
+        <v>0.00045167361398785219</v>
       </c>
       <c r="V13">
-        <v>0.00014556349198360934</v>
+        <v>0.00015002552897824662</v>
       </c>
       <c r="W13">
-        <v>-0.00022796661723335993</v>
+        <v>-0.00021996446149501973</v>
       </c>
       <c r="X13">
-        <v>-0.00024941802218425026</v>
+        <v>-0.00024244449458122675</v>
       </c>
       <c r="Y13">
-        <v>-0.00030043872716400857</v>
+        <v>-0.00029083518978950034</v>
       </c>
       <c r="Z13">
-        <v>-0.00025412350266922025</v>
+        <v>-0.00024887505658916865</v>
       </c>
       <c r="AA13">
-        <v>-0.00028770017743928798</v>
+        <v>-0.00028005638457713684</v>
       </c>
       <c r="AB13">
-        <v>-0.00020856127885315033</v>
+        <v>-0.00020339001972587178</v>
       </c>
       <c r="AC13">
-        <v>1.4548855961440797e-05</v>
+        <v>1.4648079613180153e-05</v>
       </c>
       <c r="AD13">
-        <v>-1.3244629703063927e-05</v>
+        <v>-1.5044552863043405e-05</v>
       </c>
       <c r="AE13">
-        <v>1.8165728128279783e-05</v>
+        <v>1.6109562603758331e-05</v>
       </c>
       <c r="AF13">
-        <v>0.0022686468873432813</v>
+        <v>0.0022789462033859474</v>
       </c>
     </row>
     <row r="14">
@@ -3691,97 +3691,97 @@
         <v>27</v>
       </c>
       <c r="B14">
-        <v>0.0772091447970151</v>
+        <v>0.072682851392894932</v>
       </c>
       <c r="C14">
-        <v>0.00015412556938098774</v>
+        <v>0.00011942233552537671</v>
       </c>
       <c r="D14">
-        <v>-8.7506815788145585e-05</v>
+        <v>-8.1319415389565462e-05</v>
       </c>
       <c r="E14">
-        <v>6.4323715881421417e-07</v>
+        <v>6.0846141394254764e-07</v>
       </c>
       <c r="F14">
-        <v>-2.0086948044259305e-05</v>
+        <v>-2.5411319357183417e-05</v>
       </c>
       <c r="G14">
-        <v>2.4205367652443879e-05</v>
+        <v>2.8065530651967974e-05</v>
       </c>
       <c r="H14">
-        <v>-3.8522040883761852e-05</v>
+        <v>-4.6698585106363228e-05</v>
       </c>
       <c r="I14">
-        <v>0.00013391735913121093</v>
+        <v>0.00012999567124037076</v>
       </c>
       <c r="J14">
-        <v>-8.8772564008486165e-05</v>
+        <v>-7.098638285532935e-05</v>
       </c>
       <c r="K14">
-        <v>0.0013192664166903128</v>
+        <v>0.0013125258090180498</v>
       </c>
       <c r="L14">
-        <v>0.00016064099398632812</v>
+        <v>0.00015056530182096511</v>
       </c>
       <c r="M14">
-        <v>0.00084515597956036641</v>
+        <v>0.0008475390906643827</v>
       </c>
       <c r="N14">
-        <v>0.0015874126387094712</v>
+        <v>0.0015878241110124573</v>
       </c>
       <c r="O14">
-        <v>0.0033309980350952166</v>
+        <v>0.0033253740814743367</v>
       </c>
       <c r="P14">
-        <v>0.0026281071940719254</v>
+        <v>0.0026192812688955011</v>
       </c>
       <c r="Q14">
-        <v>-6.0609176290801851e-05</v>
+        <v>-5.9622122030124049e-05</v>
       </c>
       <c r="R14">
-        <v>0.00015470776933777228</v>
+        <v>8.2890003315921635e-05</v>
       </c>
       <c r="S14">
-        <v>4.9753705705128323e-05</v>
+        <v>0.00014186033712839091</v>
       </c>
       <c r="T14">
-        <v>0.00010804341930913466</v>
+        <v>2.1820419236548286e-05</v>
       </c>
       <c r="U14">
-        <v>0.00090404317481287554</v>
+        <v>0.0009190654310700431</v>
       </c>
       <c r="V14">
-        <v>7.6992634687152563e-05</v>
+        <v>7.6340792777190511e-05</v>
       </c>
       <c r="W14">
-        <v>-0.00025685675830949698</v>
+        <v>-0.00025105798887131714</v>
       </c>
       <c r="X14">
-        <v>-0.00033086972915194034</v>
+        <v>-0.00032623527497734495</v>
       </c>
       <c r="Y14">
-        <v>-0.00034348086675609502</v>
+        <v>-0.0003361037257944504</v>
       </c>
       <c r="Z14">
-        <v>-0.00021823233229966918</v>
+        <v>-0.00021536049324493009</v>
       </c>
       <c r="AA14">
-        <v>-0.00034910654710936461</v>
+        <v>-0.00034239409481394325</v>
       </c>
       <c r="AB14">
-        <v>-0.00022080638520407311</v>
+        <v>-0.00021777243440040928</v>
       </c>
       <c r="AC14">
-        <v>3.0786045339419217e-05</v>
+        <v>3.0603459678323622e-05</v>
       </c>
       <c r="AD14">
-        <v>-7.2938601358510553e-05</v>
+        <v>-7.6728373431216371e-05</v>
       </c>
       <c r="AE14">
-        <v>-6.0624952156468261e-05</v>
+        <v>-6.0861654323060739e-05</v>
       </c>
       <c r="AF14">
-        <v>-0.00061661017433234378</v>
+        <v>-0.00082375056725186857</v>
       </c>
     </row>
     <row r="15">
@@ -3789,97 +3789,97 @@
         <v>28</v>
       </c>
       <c r="B15">
-        <v>0.15526123972573094</v>
+        <v>0.15058340100915391</v>
       </c>
       <c r="C15">
-        <v>0.00012724761698980827</v>
+        <v>0.00011547551740743927</v>
       </c>
       <c r="D15">
-        <v>-0.00018659072133111153</v>
+        <v>-0.00018703019726721941</v>
       </c>
       <c r="E15">
-        <v>1.4353804087846752e-06</v>
+        <v>1.4432278013997932e-06</v>
       </c>
       <c r="F15">
-        <v>0.00013679014965022485</v>
+        <v>0.00012613560276452523</v>
       </c>
       <c r="G15">
-        <v>0.00015193521622598218</v>
+        <v>0.00015498686885990869</v>
       </c>
       <c r="H15">
-        <v>0.00034026502123803213</v>
+        <v>0.00033649144332574543</v>
       </c>
       <c r="I15">
-        <v>0.00056354778732926631</v>
+        <v>0.00056161171625847804</v>
       </c>
       <c r="J15">
-        <v>-0.0002435896369688776</v>
+        <v>-0.00023381371213415658</v>
       </c>
       <c r="K15">
-        <v>0.0013209334027606951</v>
+        <v>0.0013115516340900695</v>
       </c>
       <c r="L15">
-        <v>0.0002517259728055572</v>
+        <v>0.00024873667104816739</v>
       </c>
       <c r="M15">
-        <v>0.00085879000544015235</v>
+        <v>0.00086181643411142026</v>
       </c>
       <c r="N15">
-        <v>0.0016975543070582313</v>
+        <v>0.0016971493001531265</v>
       </c>
       <c r="O15">
-        <v>0.0026281071940719254</v>
+        <v>0.0026192812688955011</v>
       </c>
       <c r="P15">
-        <v>0.0036953065976039982</v>
+        <v>0.0036861282889782644</v>
       </c>
       <c r="Q15">
-        <v>2.1477023856255212e-05</v>
+        <v>2.4060358673338626e-05</v>
       </c>
       <c r="R15">
-        <v>8.5486696451647832e-05</v>
+        <v>5.7202121184093968e-05</v>
       </c>
       <c r="S15">
-        <v>-3.4861246310112569e-05</v>
+        <v>3.7473955108548998e-05</v>
       </c>
       <c r="T15">
-        <v>9.5855110387021297e-06</v>
+        <v>1.348479476101028e-05</v>
       </c>
       <c r="U15">
-        <v>0.0011246650520041418</v>
+        <v>0.0011281194748449643</v>
       </c>
       <c r="V15">
-        <v>2.1531454714899612e-05</v>
+        <v>2.3381858180763701e-05</v>
       </c>
       <c r="W15">
-        <v>-0.00019175661010680575</v>
+        <v>-0.00018873634597326491</v>
       </c>
       <c r="X15">
-        <v>-0.00040795362771711089</v>
+        <v>-0.00040550502924804237</v>
       </c>
       <c r="Y15">
-        <v>-0.00034378450321511007</v>
+        <v>-0.00034081909917388657</v>
       </c>
       <c r="Z15">
-        <v>-0.00019388571336950797</v>
+        <v>-0.00019405216603030507</v>
       </c>
       <c r="AA15">
-        <v>-0.00032793406210695315</v>
+        <v>-0.00032387872231870365</v>
       </c>
       <c r="AB15">
-        <v>-0.00015545698381863246</v>
+        <v>-0.00015439345875577432</v>
       </c>
       <c r="AC15">
-        <v>2.900263651559643e-05</v>
+        <v>2.8749809877302813e-05</v>
       </c>
       <c r="AD15">
-        <v>-6.7969074724705996e-05</v>
+        <v>-6.9070441358058026e-05</v>
       </c>
       <c r="AE15">
-        <v>6.3133461328519595e-06</v>
+        <v>7.8556709443727314e-06</v>
       </c>
       <c r="AF15">
-        <v>0.0018750322611581632</v>
+        <v>0.0018947356936218698</v>
       </c>
     </row>
     <row r="16">
@@ -3887,97 +3887,97 @@
         <v>29</v>
       </c>
       <c r="B16">
-        <v>0.70039811024406151</v>
+        <v>0.69699352119333824</v>
       </c>
       <c r="C16">
-        <v>-0.00041912642414828775</v>
+        <v>-0.00042326165195228981</v>
       </c>
       <c r="D16">
-        <v>-0.00020851444792344175</v>
+        <v>-0.00020887139217288945</v>
       </c>
       <c r="E16">
-        <v>1.8037157605078595e-06</v>
+        <v>1.8094565872085687e-06</v>
       </c>
       <c r="F16">
-        <v>0.00017392951375968559</v>
+        <v>0.00017638354082061833</v>
       </c>
       <c r="G16">
-        <v>0.00016886192199491246</v>
+        <v>0.00017383092497874272</v>
       </c>
       <c r="H16">
-        <v>5.6725075104128005e-05</v>
+        <v>5.6744577319602142e-05</v>
       </c>
       <c r="I16">
-        <v>1.3093487704130687e-05</v>
+        <v>1.3745747940808854e-05</v>
       </c>
       <c r="J16">
-        <v>-0.00036335595410660546</v>
+        <v>-0.00036123510642958163</v>
       </c>
       <c r="K16">
-        <v>-0.00079499645727432059</v>
+        <v>-0.00079344262078678396</v>
       </c>
       <c r="L16">
-        <v>0.00020502767681666902</v>
+        <v>0.00020245654437918447</v>
       </c>
       <c r="M16">
-        <v>-2.8053886209039567e-05</v>
+        <v>-2.4454183319798611e-05</v>
       </c>
       <c r="N16">
-        <v>-9.4906574066254984e-05</v>
+        <v>-9.2968393790273808e-05</v>
       </c>
       <c r="O16">
-        <v>-6.0609176290801851e-05</v>
+        <v>-5.9622122030124049e-05</v>
       </c>
       <c r="P16">
-        <v>2.1477023856255212e-05</v>
+        <v>2.4060358673338626e-05</v>
       </c>
       <c r="Q16">
-        <v>0.0020251351429110506</v>
+        <v>0.0020263887279008746</v>
       </c>
       <c r="R16">
-        <v>7.7412795257932054e-05</v>
+        <v>6.5070232064915541e-05</v>
       </c>
       <c r="S16">
-        <v>-5.5950405445270949e-05</v>
+        <v>-2.8370685089056883e-06</v>
       </c>
       <c r="T16">
-        <v>-1.0271487050409834e-05</v>
+        <v>9.4704023656464191e-06</v>
       </c>
       <c r="U16">
-        <v>5.5314154604624837e-05</v>
+        <v>5.9004889913628268e-05</v>
       </c>
       <c r="V16">
-        <v>-0.00028653459268976279</v>
+        <v>-0.00029070223405364387</v>
       </c>
       <c r="W16">
-        <v>0.00031952292265807682</v>
+        <v>0.00031426355071809928</v>
       </c>
       <c r="X16">
-        <v>0.00030820624492360993</v>
+        <v>0.00030083896246165551</v>
       </c>
       <c r="Y16">
-        <v>0.00041541802196723128</v>
+        <v>0.00040775648551883732</v>
       </c>
       <c r="Z16">
-        <v>0.00044002168029325421</v>
+        <v>0.00043272826800487568</v>
       </c>
       <c r="AA16">
-        <v>0.00022695569696376585</v>
+        <v>0.00022044725784620934</v>
       </c>
       <c r="AB16">
-        <v>0.0003164770103205837</v>
+        <v>0.00030965431843519556</v>
       </c>
       <c r="AC16">
-        <v>-2.7909371255910195e-06</v>
+        <v>-2.8648510659164898e-06</v>
       </c>
       <c r="AD16">
-        <v>-5.8552944791506577e-05</v>
+        <v>-5.9196877903071657e-05</v>
       </c>
       <c r="AE16">
-        <v>-2.0434884494165411e-05</v>
+        <v>-2.0531197943280403e-05</v>
       </c>
       <c r="AF16">
-        <v>0.0060889401524989763</v>
+        <v>0.006096500656888419</v>
       </c>
     </row>
     <row r="17">
@@ -3985,97 +3985,97 @@
         <v>46</v>
       </c>
       <c r="B17">
-        <v>-0.091440507807326071</v>
+        <v>-0.18001015393793976</v>
       </c>
       <c r="C17">
-        <v>0.00078794856558135076</v>
+        <v>0.00067479034677417641</v>
       </c>
       <c r="D17">
-        <v>0.0001459489014538802</v>
+        <v>0.00033549961559651859</v>
       </c>
       <c r="E17">
-        <v>-1.4848012337321137e-06</v>
+        <v>-3.0130221747405795e-06</v>
       </c>
       <c r="F17">
-        <v>0.00035359481747339761</v>
+        <v>0.0005334614974869048</v>
       </c>
       <c r="G17">
-        <v>0.00019957995172552832</v>
+        <v>0.00039766183659994004</v>
       </c>
       <c r="H17">
-        <v>4.3471605720680405e-05</v>
+        <v>2.7001880979072185e-05</v>
       </c>
       <c r="I17">
-        <v>-1.3775472791114062e-05</v>
+        <v>-5.0477405441336413e-05</v>
       </c>
       <c r="J17">
-        <v>-0.00069186153377019926</v>
+        <v>-0.00071843000749185126</v>
       </c>
       <c r="K17">
-        <v>0.0001345809428470013</v>
+        <v>0.00016357534692175877</v>
       </c>
       <c r="L17">
-        <v>-0.00024242249362033922</v>
+        <v>-0.00042244178030889353</v>
       </c>
       <c r="M17">
-        <v>-4.5460339183357929e-05</v>
+        <v>-4.6234290833055967e-05</v>
       </c>
       <c r="N17">
-        <v>-5.5509477907005772e-06</v>
+        <v>-2.4854932899001718e-05</v>
       </c>
       <c r="O17">
-        <v>0.00015470776933777228</v>
+        <v>8.2890003315921635e-05</v>
       </c>
       <c r="P17">
-        <v>8.5486696451647832e-05</v>
+        <v>5.7202121184093968e-05</v>
       </c>
       <c r="Q17">
-        <v>7.7412795257932054e-05</v>
+        <v>6.5070232064915541e-05</v>
       </c>
       <c r="R17">
-        <v>0.0025516176036147107</v>
+        <v>0.0027652518618685278</v>
       </c>
       <c r="S17">
-        <v>-0.0014669726564043183</v>
+        <v>-0.0017887970744277814</v>
       </c>
       <c r="T17">
-        <v>-0.0014062077033850031</v>
+        <v>-0.0015953009365758301</v>
       </c>
       <c r="U17">
-        <v>-0.00038217195501605099</v>
+        <v>-0.00034638816861697649</v>
       </c>
       <c r="V17">
-        <v>0.00039059838023810265</v>
+        <v>0.0003883545172748969</v>
       </c>
       <c r="W17">
-        <v>0.00013085887932505458</v>
+        <v>0.00012121926822444319</v>
       </c>
       <c r="X17">
-        <v>4.3387426228939062e-05</v>
+        <v>3.4437390712475403e-05</v>
       </c>
       <c r="Y17">
-        <v>0.00015536182369949356</v>
+        <v>0.0001467512952495688</v>
       </c>
       <c r="Z17">
-        <v>0.00018135024026671694</v>
+        <v>0.00012784028704198366</v>
       </c>
       <c r="AA17">
-        <v>0.00011683960778865706</v>
+        <v>0.0001192564933582504</v>
       </c>
       <c r="AB17">
-        <v>0.00015333264016528103</v>
+        <v>0.00013048039836500384</v>
       </c>
       <c r="AC17">
-        <v>4.7143973248359785e-06</v>
+        <v>1.0884319646008893e-08</v>
       </c>
       <c r="AD17">
-        <v>6.0870600581627811e-05</v>
+        <v>6.0972931589001102e-05</v>
       </c>
       <c r="AE17">
-        <v>4.8794614115166062e-05</v>
+        <v>8.481826988177444e-05</v>
       </c>
       <c r="AF17">
-        <v>-0.0043589147659581773</v>
+        <v>-0.0099367354861983545</v>
       </c>
     </row>
     <row r="18">
@@ -4083,97 +4083,97 @@
         <v>47</v>
       </c>
       <c r="B18">
-        <v>0.19690863233773628</v>
+        <v>0.20230510212742045</v>
       </c>
       <c r="C18">
-        <v>-0.00022511761873168627</v>
+        <v>-0.00029874274436318573</v>
       </c>
       <c r="D18">
-        <v>-0.00027466335224897356</v>
+        <v>-0.00021927914050563421</v>
       </c>
       <c r="E18">
-        <v>2.2750375750720358e-06</v>
+        <v>1.6623732069506259e-06</v>
       </c>
       <c r="F18">
-        <v>-0.00050320506515459662</v>
+        <v>-0.0010446205190958319</v>
       </c>
       <c r="G18">
-        <v>-0.00041744464422944529</v>
+        <v>-0.0009321461225941137</v>
       </c>
       <c r="H18">
-        <v>-2.2661785328908856e-05</v>
+        <v>-3.5516595288080091e-05</v>
       </c>
       <c r="I18">
-        <v>6.6612424270576779e-05</v>
+        <v>0.00011539642106720392</v>
       </c>
       <c r="J18">
-        <v>0.0003826454553538328</v>
+        <v>0.00076959633285667885</v>
       </c>
       <c r="K18">
-        <v>-0.0001553246597402212</v>
+        <v>-0.00031190163130372849</v>
       </c>
       <c r="L18">
-        <v>0.00053434800485357092</v>
+        <v>0.00081219011060027499</v>
       </c>
       <c r="M18">
-        <v>5.3963192933774505e-06</v>
+        <v>7.1503245069130675e-05</v>
       </c>
       <c r="N18">
-        <v>5.019249659759422e-05</v>
+        <v>-2.2702103437804316e-05</v>
       </c>
       <c r="O18">
-        <v>4.9753705705128323e-05</v>
+        <v>0.00014186033712839091</v>
       </c>
       <c r="P18">
-        <v>-3.4861246310112569e-05</v>
+        <v>3.7473955108548998e-05</v>
       </c>
       <c r="Q18">
-        <v>-5.5950405445270949e-05</v>
+        <v>-2.8370685089056883e-06</v>
       </c>
       <c r="R18">
-        <v>-0.0014669726564043183</v>
+        <v>-0.0017887970744277814</v>
       </c>
       <c r="S18">
-        <v>0.0044398038482355694</v>
+        <v>0.0063400322917872131</v>
       </c>
       <c r="T18">
-        <v>0.001193949137042077</v>
+        <v>0.001423299510050689</v>
       </c>
       <c r="U18">
-        <v>0.00018584129691221309</v>
+        <v>0.00010268980970879458</v>
       </c>
       <c r="V18">
-        <v>-0.00022725626399189443</v>
+        <v>-0.00024070265918691553</v>
       </c>
       <c r="W18">
-        <v>-3.4002197660835606e-05</v>
+        <v>-9.0096142385287167e-05</v>
       </c>
       <c r="X18">
-        <v>7.5752914376313492e-05</v>
+        <v>-2.3687929021631859e-05</v>
       </c>
       <c r="Y18">
-        <v>3.2801598417574011e-05</v>
+        <v>9.3603901718592852e-05</v>
       </c>
       <c r="Z18">
-        <v>-6.4812539956370444e-06</v>
+        <v>-2.7170147437050388e-05</v>
       </c>
       <c r="AA18">
-        <v>3.2374485291783483e-05</v>
+        <v>-3.1612628740141854e-05</v>
       </c>
       <c r="AB18">
-        <v>-2.9013127443377508e-05</v>
+        <v>8.5678058381575238e-05</v>
       </c>
       <c r="AC18">
-        <v>3.0286934443505986e-06</v>
+        <v>1.5624033055573806e-05</v>
       </c>
       <c r="AD18">
-        <v>-0.00011249496239385979</v>
+        <v>-0.00017872411875424592</v>
       </c>
       <c r="AE18">
-        <v>-8.3169900872820044e-05</v>
+        <v>-0.00016821745419701769</v>
       </c>
       <c r="AF18">
-        <v>0.0083108403005202891</v>
+        <v>0.0070811416908349023</v>
       </c>
     </row>
     <row r="19">
@@ -4181,97 +4181,97 @@
         <v>48</v>
       </c>
       <c r="B19">
-        <v>0.13574285166008893</v>
+        <v>0.20846442851149286</v>
       </c>
       <c r="C19">
-        <v>-0.00029401555776640111</v>
+        <v>-0.00012882799477750343</v>
       </c>
       <c r="D19">
-        <v>-5.5695224003948773e-05</v>
+        <v>-0.00047693563485250515</v>
       </c>
       <c r="E19">
-        <v>3.0226665811251352e-07</v>
+        <v>3.984075981260774e-06</v>
       </c>
       <c r="F19">
-        <v>-0.00093313740148424571</v>
+        <v>-0.00051706008620285709</v>
       </c>
       <c r="G19">
-        <v>-0.00080820040715199812</v>
+        <v>-0.0005128743988593509</v>
       </c>
       <c r="H19">
-        <v>-5.7469043889428104e-05</v>
+        <v>3.8815558325247458e-05</v>
       </c>
       <c r="I19">
-        <v>7.8908114838060215e-05</v>
+        <v>6.8919768821180149e-05</v>
       </c>
       <c r="J19">
-        <v>0.00071909823055051753</v>
+        <v>0.00046056870370207292</v>
       </c>
       <c r="K19">
-        <v>-0.00029534533075805758</v>
+        <v>-8.7108686529680239e-05</v>
       </c>
       <c r="L19">
-        <v>0.00069419497770139551</v>
+        <v>0.00033389148418677141</v>
       </c>
       <c r="M19">
-        <v>6.2339736771488885e-05</v>
+        <v>4.7584987379977188e-05</v>
       </c>
       <c r="N19">
-        <v>-4.2348101070800487e-05</v>
+        <v>2.1865485366483043e-05</v>
       </c>
       <c r="O19">
-        <v>0.00010804341930913466</v>
+        <v>2.1820419236548286e-05</v>
       </c>
       <c r="P19">
-        <v>9.5855110387021297e-06</v>
+        <v>1.348479476101028e-05</v>
       </c>
       <c r="Q19">
-        <v>-1.0271487050409834e-05</v>
+        <v>9.4704023656464191e-06</v>
       </c>
       <c r="R19">
-        <v>-0.0014062077033850031</v>
+        <v>-0.0015953009365758301</v>
       </c>
       <c r="S19">
-        <v>0.001193949137042077</v>
+        <v>0.001423299510050689</v>
       </c>
       <c r="T19">
-        <v>0.0060361572838891044</v>
+        <v>0.004794871695148104</v>
       </c>
       <c r="U19">
-        <v>0.00010367218748962481</v>
+        <v>2.0086170280672914e-05</v>
       </c>
       <c r="V19">
-        <v>-0.0002171365028712036</v>
+        <v>-0.00012204080069225373</v>
       </c>
       <c r="W19">
-        <v>-5.6459651957089033e-05</v>
+        <v>-4.8482046843859386e-05</v>
       </c>
       <c r="X19">
-        <v>-3.5487735153185568e-07</v>
+        <v>-6.6372444596110233e-05</v>
       </c>
       <c r="Y19">
-        <v>0.00012812588710301581</v>
+        <v>-0.00015413901220451406</v>
       </c>
       <c r="Z19">
-        <v>-2.417736306926585e-05</v>
+        <v>2.2633020274732615e-05</v>
       </c>
       <c r="AA19">
-        <v>2.4388886001330216e-05</v>
+        <v>-0.00012648232008996389</v>
       </c>
       <c r="AB19">
-        <v>0.00011918428849947609</v>
+        <v>-2.6678346156877066e-05</v>
       </c>
       <c r="AC19">
-        <v>1.3435094568229044e-05</v>
+        <v>5.5367129802432136e-06</v>
       </c>
       <c r="AD19">
-        <v>-0.00019424870032547529</v>
+        <v>7.5151238037992826e-05</v>
       </c>
       <c r="AE19">
-        <v>-0.00015139558668159948</v>
+        <v>-5.1538663644032368e-05</v>
       </c>
       <c r="AF19">
-        <v>0.0022384526513898467</v>
+        <v>0.014227122448520785</v>
       </c>
     </row>
     <row r="20">
@@ -4279,97 +4279,97 @@
         <v>49</v>
       </c>
       <c r="B20">
-        <v>0.10241601649597953</v>
+        <v>0.10975265556717631</v>
       </c>
       <c r="C20">
-        <v>-5.993302321163045e-05</v>
+        <v>-4.3888650747473957e-05</v>
       </c>
       <c r="D20">
-        <v>-8.3519287051491732e-05</v>
+        <v>-8.7403088317757407e-05</v>
       </c>
       <c r="E20">
-        <v>6.0524281928056372e-07</v>
+        <v>6.3141847957079455e-07</v>
       </c>
       <c r="F20">
-        <v>1.3152189557902143e-05</v>
+        <v>2.754369199701838e-06</v>
       </c>
       <c r="G20">
-        <v>4.906263521241034e-05</v>
+        <v>3.5950533332993959e-05</v>
       </c>
       <c r="H20">
-        <v>-1.4416054766716179e-05</v>
+        <v>-1.5690043718079186e-05</v>
       </c>
       <c r="I20">
-        <v>1.5554265670880837e-06</v>
+        <v>3.1646010236562169e-06</v>
       </c>
       <c r="J20">
-        <v>-8.5727475420305406e-05</v>
+        <v>-9.9701994357434716e-05</v>
       </c>
       <c r="K20">
-        <v>0.00035870791963787355</v>
+        <v>0.00035376683292267808</v>
       </c>
       <c r="L20">
-        <v>0.00013409338565726183</v>
+        <v>0.00015073419211822446</v>
       </c>
       <c r="M20">
-        <v>5.9191160134951845e-05</v>
+        <v>5.6004843837205204e-05</v>
       </c>
       <c r="N20">
-        <v>0.00044926220063263363</v>
+        <v>0.00045167361398785219</v>
       </c>
       <c r="O20">
-        <v>0.00090404317481287554</v>
+        <v>0.0009190654310700431</v>
       </c>
       <c r="P20">
-        <v>0.0011246650520041418</v>
+        <v>0.0011281194748449643</v>
       </c>
       <c r="Q20">
-        <v>5.5314154604624837e-05</v>
+        <v>5.9004889913628268e-05</v>
       </c>
       <c r="R20">
-        <v>-0.00038217195501605099</v>
+        <v>-0.00034638816861697649</v>
       </c>
       <c r="S20">
-        <v>0.00018584129691221309</v>
+        <v>0.00010268980970879458</v>
       </c>
       <c r="T20">
-        <v>0.00010367218748962481</v>
+        <v>2.0086170280672914e-05</v>
       </c>
       <c r="U20">
-        <v>0.0014400396157607225</v>
+        <v>0.0014338082258748598</v>
       </c>
       <c r="V20">
-        <v>-0.00038707329911725092</v>
+        <v>-0.00037669489887032356</v>
       </c>
       <c r="W20">
-        <v>8.1187177557658172e-05</v>
+        <v>8.6277608255261318e-05</v>
       </c>
       <c r="X20">
-        <v>4.1355961610113233e-05</v>
+        <v>4.6019033076032806e-05</v>
       </c>
       <c r="Y20">
-        <v>3.3519444259469817e-05</v>
+        <v>4.3922389092400556e-05</v>
       </c>
       <c r="Z20">
-        <v>3.9544232753743009e-06</v>
+        <v>1.1918264766500042e-05</v>
       </c>
       <c r="AA20">
-        <v>1.2193991519297951e-05</v>
+        <v>2.0337663410299181e-05</v>
       </c>
       <c r="AB20">
-        <v>-1.568933238852414e-05</v>
+        <v>-1.0155547831822251e-05</v>
       </c>
       <c r="AC20">
-        <v>1.9161655377142548e-05</v>
+        <v>1.9886218302450158e-05</v>
       </c>
       <c r="AD20">
-        <v>-2.6469572485578251e-05</v>
+        <v>-3.1775308139086621e-05</v>
       </c>
       <c r="AE20">
-        <v>1.1721360213440366e-05</v>
+        <v>6.0271614670592616e-06</v>
       </c>
       <c r="AF20">
-        <v>0.00092174241503439544</v>
+        <v>0.0010161438826846517</v>
       </c>
     </row>
     <row r="21">
@@ -4377,97 +4377,97 @@
         <v>50</v>
       </c>
       <c r="B21">
-        <v>-0.089575253778909236</v>
+        <v>-0.095214537267864593</v>
       </c>
       <c r="C21">
-        <v>0.00012888864281596204</v>
+        <v>0.00011905073398588788</v>
       </c>
       <c r="D21">
-        <v>-5.6131187514539549e-05</v>
+        <v>-3.9630962419177907e-05</v>
       </c>
       <c r="E21">
-        <v>4.9716219899972034e-07</v>
+        <v>3.6666186084683935e-07</v>
       </c>
       <c r="F21">
-        <v>6.306579232923798e-05</v>
+        <v>7.7288522244261734e-05</v>
       </c>
       <c r="G21">
-        <v>0.00010101082290138452</v>
+        <v>0.00011735735905567344</v>
       </c>
       <c r="H21">
-        <v>5.7839320015892922e-05</v>
+        <v>5.4984855633013877e-05</v>
       </c>
       <c r="I21">
-        <v>-1.5639148942113326e-06</v>
+        <v>-3.3708711019775415e-06</v>
       </c>
       <c r="J21">
-        <v>-0.00018228392450622168</v>
+        <v>-0.00018217420460480294</v>
       </c>
       <c r="K21">
-        <v>-5.0795873741489768e-05</v>
+        <v>-4.6484309492659213e-05</v>
       </c>
       <c r="L21">
-        <v>9.8889032875812541e-05</v>
+        <v>9.0337666218841175e-05</v>
       </c>
       <c r="M21">
-        <v>7.8117580987995206e-05</v>
+        <v>7.7953104558420858e-05</v>
       </c>
       <c r="N21">
-        <v>0.00014556349198360934</v>
+        <v>0.00015002552897824662</v>
       </c>
       <c r="O21">
-        <v>7.6992634687152563e-05</v>
+        <v>7.6340792777190511e-05</v>
       </c>
       <c r="P21">
-        <v>2.1531454714899612e-05</v>
+        <v>2.3381858180763701e-05</v>
       </c>
       <c r="Q21">
-        <v>-0.00028653459268976279</v>
+        <v>-0.00029070223405364387</v>
       </c>
       <c r="R21">
-        <v>0.00039059838023810265</v>
+        <v>0.0003883545172748969</v>
       </c>
       <c r="S21">
-        <v>-0.00022725626399189443</v>
+        <v>-0.00024070265918691553</v>
       </c>
       <c r="T21">
-        <v>-0.0002171365028712036</v>
+        <v>-0.00012204080069225373</v>
       </c>
       <c r="U21">
-        <v>-0.00038707329911725092</v>
+        <v>-0.00037669489887032356</v>
       </c>
       <c r="V21">
-        <v>0.0041999028039556331</v>
+        <v>0.0042159126883528023</v>
       </c>
       <c r="W21">
-        <v>6.4804282601003699e-05</v>
+        <v>6.6728005251545132e-05</v>
       </c>
       <c r="X21">
-        <v>0.00015284707775118723</v>
+        <v>0.00015637276049661658</v>
       </c>
       <c r="Y21">
-        <v>1.4279562944136283e-05</v>
+        <v>1.6367861033354371e-05</v>
       </c>
       <c r="Z21">
-        <v>0.00013021739258220867</v>
+        <v>0.00012900647662039927</v>
       </c>
       <c r="AA21">
-        <v>4.1623959418040041e-05</v>
+        <v>4.6779451483714639e-05</v>
       </c>
       <c r="AB21">
-        <v>6.1840868144289005e-05</v>
+        <v>6.1309649792859797e-05</v>
       </c>
       <c r="AC21">
-        <v>1.2279161423655032e-06</v>
+        <v>1.2533754994691592e-06</v>
       </c>
       <c r="AD21">
-        <v>1.4801331372515415e-05</v>
+        <v>1.0683123865898217e-05</v>
       </c>
       <c r="AE21">
-        <v>-8.643213029227865e-05</v>
+        <v>-8.60921585123263e-05</v>
       </c>
       <c r="AF21">
-        <v>0.0013660439129549486</v>
+        <v>0.00085672300024444877</v>
       </c>
     </row>
     <row r="22">
@@ -4475,97 +4475,97 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>0.24206049386872983</v>
+        <v>0.23991662873098083</v>
       </c>
       <c r="C22">
-        <v>0.00013345126425377005</v>
+        <v>0.00012246231362551363</v>
       </c>
       <c r="D22">
-        <v>-6.7465016128392952e-05</v>
+        <v>-5.6088664379352893e-05</v>
       </c>
       <c r="E22">
-        <v>6.662090024405409e-07</v>
+        <v>5.8161907022155884e-07</v>
       </c>
       <c r="F22">
-        <v>0.00014470626196641523</v>
+        <v>0.00015317646621142156</v>
       </c>
       <c r="G22">
-        <v>5.7965831031604742e-05</v>
+        <v>5.5624645884946866e-05</v>
       </c>
       <c r="H22">
-        <v>8.9744080367285635e-05</v>
+        <v>8.4693385359520821e-05</v>
       </c>
       <c r="I22">
-        <v>-0.0001511264226981817</v>
+        <v>-0.00015199253212248224</v>
       </c>
       <c r="J22">
-        <v>-0.00016425174750533955</v>
+        <v>-0.00016400049026041308</v>
       </c>
       <c r="K22">
-        <v>-0.00021145918025485661</v>
+        <v>-0.00020626614274486159</v>
       </c>
       <c r="L22">
-        <v>7.9520853194377586e-05</v>
+        <v>6.7893106911379349e-05</v>
       </c>
       <c r="M22">
-        <v>-0.00014858500685012086</v>
+        <v>-0.00014442909588583091</v>
       </c>
       <c r="N22">
-        <v>-0.00022796661723335993</v>
+        <v>-0.00021996446149501973</v>
       </c>
       <c r="O22">
-        <v>-0.00025685675830949698</v>
+        <v>-0.00025105798887131714</v>
       </c>
       <c r="P22">
-        <v>-0.00019175661010680575</v>
+        <v>-0.00018873634597326491</v>
       </c>
       <c r="Q22">
-        <v>0.00031952292265807682</v>
+        <v>0.00031426355071809928</v>
       </c>
       <c r="R22">
-        <v>0.00013085887932505458</v>
+        <v>0.00012121926822444319</v>
       </c>
       <c r="S22">
-        <v>-3.4002197660835606e-05</v>
+        <v>-9.0096142385287167e-05</v>
       </c>
       <c r="T22">
-        <v>-5.6459651957089033e-05</v>
+        <v>-4.8482046843859386e-05</v>
       </c>
       <c r="U22">
-        <v>8.1187177557658172e-05</v>
+        <v>8.6277608255261318e-05</v>
       </c>
       <c r="V22">
-        <v>6.4804282601003699e-05</v>
+        <v>6.6728005251545132e-05</v>
       </c>
       <c r="W22">
-        <v>0.0065553899059784372</v>
+        <v>0.006565999906691578</v>
       </c>
       <c r="X22">
-        <v>0.005577516625327475</v>
+        <v>0.0055886845572016754</v>
       </c>
       <c r="Y22">
-        <v>0.0055693492150370606</v>
+        <v>0.0055836897298863347</v>
       </c>
       <c r="Z22">
-        <v>0.0056003550254638841</v>
+        <v>0.0056096126105041749</v>
       </c>
       <c r="AA22">
-        <v>0.0055900887204728437</v>
+        <v>0.0056020299962277319</v>
       </c>
       <c r="AB22">
-        <v>0.005565013506240675</v>
+        <v>0.0055751490951724235</v>
       </c>
       <c r="AC22">
-        <v>2.4294431255898242e-06</v>
+        <v>2.2049455490788755e-06</v>
       </c>
       <c r="AD22">
-        <v>2.1212966939832944e-05</v>
+        <v>1.8804419656084275e-05</v>
       </c>
       <c r="AE22">
-        <v>4.3754300290579744e-05</v>
+        <v>4.5988420942344845e-05</v>
       </c>
       <c r="AF22">
-        <v>-0.0038754806573304476</v>
+        <v>-0.0042507347105164121</v>
       </c>
     </row>
     <row r="23">
@@ -4573,97 +4573,97 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>0.25977719823249595</v>
+        <v>0.25624357551963872</v>
       </c>
       <c r="C23">
-        <v>0.00013106945136016793</v>
+        <v>0.00011841634004566988</v>
       </c>
       <c r="D23">
-        <v>9.7113256569275608e-06</v>
+        <v>2.3621705846563201e-05</v>
       </c>
       <c r="E23">
-        <v>1.38548718467261e-07</v>
+        <v>3.2856827072145524e-08</v>
       </c>
       <c r="F23">
-        <v>0.0001435653601878778</v>
+        <v>0.00014883785957289786</v>
       </c>
       <c r="G23">
-        <v>-2.5862671698198558e-06</v>
+        <v>-6.1543642715794489e-06</v>
       </c>
       <c r="H23">
-        <v>0.00010561664733128601</v>
+        <v>0.00010227449040021161</v>
       </c>
       <c r="I23">
-        <v>-0.00011572734246231332</v>
+        <v>-0.00011537836761782016</v>
       </c>
       <c r="J23">
-        <v>-0.00015029601914325758</v>
+        <v>-0.00014747596137238556</v>
       </c>
       <c r="K23">
-        <v>-0.00029710069986508885</v>
+        <v>-0.00029102294568792721</v>
       </c>
       <c r="L23">
-        <v>2.2787685722563608e-05</v>
+        <v>9.1786741238915684e-06</v>
       </c>
       <c r="M23">
-        <v>-0.000102968327912793</v>
+        <v>-0.00010044767566196326</v>
       </c>
       <c r="N23">
-        <v>-0.00024941802218425026</v>
+        <v>-0.00024244449458122675</v>
       </c>
       <c r="O23">
-        <v>-0.00033086972915194034</v>
+        <v>-0.00032623527497734495</v>
       </c>
       <c r="P23">
-        <v>-0.00040795362771711089</v>
+        <v>-0.00040550502924804237</v>
       </c>
       <c r="Q23">
-        <v>0.00030820624492360993</v>
+        <v>0.00030083896246165551</v>
       </c>
       <c r="R23">
-        <v>4.3387426228939062e-05</v>
+        <v>3.4437390712475403e-05</v>
       </c>
       <c r="S23">
-        <v>7.5752914376313492e-05</v>
+        <v>-2.3687929021631859e-05</v>
       </c>
       <c r="T23">
-        <v>-3.5487735153185568e-07</v>
+        <v>-6.6372444596110233e-05</v>
       </c>
       <c r="U23">
-        <v>4.1355961610113233e-05</v>
+        <v>4.6019033076032806e-05</v>
       </c>
       <c r="V23">
-        <v>0.00015284707775118723</v>
+        <v>0.00015637276049661658</v>
       </c>
       <c r="W23">
-        <v>0.005577516625327475</v>
+        <v>0.0055886845572016754</v>
       </c>
       <c r="X23">
-        <v>0.0065646968334980276</v>
+        <v>0.0065739828603584996</v>
       </c>
       <c r="Y23">
-        <v>0.0055875662533152962</v>
+        <v>0.005603033708659738</v>
       </c>
       <c r="Z23">
-        <v>0.005588998046554443</v>
+        <v>0.0055975466463629043</v>
       </c>
       <c r="AA23">
-        <v>0.005594063523029282</v>
+        <v>0.0056063691318284118</v>
       </c>
       <c r="AB23">
-        <v>0.0055470854162039032</v>
+        <v>0.0055571625800598769</v>
       </c>
       <c r="AC23">
-        <v>3.1124652425375121e-06</v>
+        <v>2.8547976749440013e-06</v>
       </c>
       <c r="AD23">
-        <v>3.9751670041318415e-05</v>
+        <v>3.6772286860930646e-05</v>
       </c>
       <c r="AE23">
-        <v>1.4410669271689358e-05</v>
+        <v>1.5565115333169384e-05</v>
       </c>
       <c r="AF23">
-        <v>-0.0064913397276946706</v>
+        <v>-0.0069392962608397398</v>
       </c>
     </row>
     <row r="24">
@@ -4671,97 +4671,97 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>0.14695251080773772</v>
+        <v>0.14521188020378961</v>
       </c>
       <c r="C24">
-        <v>7.3175256894544811e-05</v>
+        <v>5.3230216531714952e-05</v>
       </c>
       <c r="D24">
-        <v>-2.7242360513751035e-05</v>
+        <v>1.2143799227627705e-06</v>
       </c>
       <c r="E24">
-        <v>2.4592369572416545e-07</v>
+        <v>2.6728374349146034e-08</v>
       </c>
       <c r="F24">
-        <v>4.6333843239345501e-05</v>
+        <v>6.0600137503937987e-05</v>
       </c>
       <c r="G24">
-        <v>-4.3240048640454457e-05</v>
+        <v>-4.5158532275312371e-05</v>
       </c>
       <c r="H24">
-        <v>0.0001253563055107607</v>
+        <v>0.00012191385129444571</v>
       </c>
       <c r="I24">
-        <v>2.1116077383386407e-05</v>
+        <v>2.1642693637046503e-05</v>
       </c>
       <c r="J24">
-        <v>-3.0435953866161936e-05</v>
+        <v>-2.8842142467410542e-05</v>
       </c>
       <c r="K24">
-        <v>-0.00027210251978592104</v>
+        <v>-0.00026567098142122941</v>
       </c>
       <c r="L24">
-        <v>-7.1815127635796276e-06</v>
+        <v>-2.4033414581407526e-05</v>
       </c>
       <c r="M24">
-        <v>-0.00013065368451483641</v>
+        <v>-0.00012464882319047032</v>
       </c>
       <c r="N24">
-        <v>-0.00030043872716400857</v>
+        <v>-0.00029083518978950034</v>
       </c>
       <c r="O24">
-        <v>-0.00034348086675609502</v>
+        <v>-0.0003361037257944504</v>
       </c>
       <c r="P24">
-        <v>-0.00034378450321511007</v>
+        <v>-0.00034081909917388657</v>
       </c>
       <c r="Q24">
-        <v>0.00041541802196723128</v>
+        <v>0.00040775648551883732</v>
       </c>
       <c r="R24">
-        <v>0.00015536182369949356</v>
+        <v>0.0001467512952495688</v>
       </c>
       <c r="S24">
-        <v>3.2801598417574011e-05</v>
+        <v>9.3603901718592852e-05</v>
       </c>
       <c r="T24">
-        <v>0.00012812588710301581</v>
+        <v>-0.00015413901220451406</v>
       </c>
       <c r="U24">
-        <v>3.3519444259469817e-05</v>
+        <v>4.3922389092400556e-05</v>
       </c>
       <c r="V24">
-        <v>1.4279562944136283e-05</v>
+        <v>1.6367861033354371e-05</v>
       </c>
       <c r="W24">
-        <v>0.0055693492150370606</v>
+        <v>0.0055836897298863347</v>
       </c>
       <c r="X24">
-        <v>0.0055875662533152962</v>
+        <v>0.005603033708659738</v>
       </c>
       <c r="Y24">
-        <v>0.0070873900815616904</v>
+        <v>0.0071160749970941902</v>
       </c>
       <c r="Z24">
-        <v>0.0055853909579848295</v>
+        <v>0.0055979776750722339</v>
       </c>
       <c r="AA24">
-        <v>0.0055865387760219978</v>
+        <v>0.0056023363320036202</v>
       </c>
       <c r="AB24">
-        <v>0.0055367004762778343</v>
+        <v>0.0055501722043315629</v>
       </c>
       <c r="AC24">
-        <v>1.0668804859240165e-05</v>
+        <v>1.076773712683325e-05</v>
       </c>
       <c r="AD24">
-        <v>-6.4647051522359654e-05</v>
+        <v>-6.970219717220439e-05</v>
       </c>
       <c r="AE24">
-        <v>-3.9905022356864859e-05</v>
+        <v>-4.0481782723951606e-05</v>
       </c>
       <c r="AF24">
-        <v>-0.0048444440937379825</v>
+        <v>-0.0057599498240735805</v>
       </c>
     </row>
     <row r="25">
@@ -4769,97 +4769,97 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>0.11833250328237095</v>
+        <v>0.11376422781623149</v>
       </c>
       <c r="C25">
-        <v>0.00016233783158817053</v>
+        <v>0.00013865831618414338</v>
       </c>
       <c r="D25">
-        <v>6.6150673977263819e-05</v>
+        <v>6.9302106205107461e-05</v>
       </c>
       <c r="E25">
-        <v>-3.6777087458663565e-07</v>
+        <v>-3.7698988840557685e-07</v>
       </c>
       <c r="F25">
-        <v>9.461183932895495e-05</v>
+        <v>0.0001030180871239017</v>
       </c>
       <c r="G25">
-        <v>-5.6786065210284731e-05</v>
+        <v>-5.2784243551179388e-05</v>
       </c>
       <c r="H25">
-        <v>0.00014931859647228504</v>
+        <v>0.00014436710684840757</v>
       </c>
       <c r="I25">
-        <v>-0.00014420484570888768</v>
+        <v>-0.00014584323727857406</v>
       </c>
       <c r="J25">
-        <v>-0.00014479438038654535</v>
+        <v>-0.00014158238213639318</v>
       </c>
       <c r="K25">
-        <v>-0.00025539691257208904</v>
+        <v>-0.00025171508452830624</v>
       </c>
       <c r="L25">
-        <v>4.0926054849702194e-05</v>
+        <v>3.1942064179653861e-05</v>
       </c>
       <c r="M25">
-        <v>-9.2374662380601642e-05</v>
+        <v>-9.1092954269858745e-05</v>
       </c>
       <c r="N25">
-        <v>-0.00025412350266922025</v>
+        <v>-0.00024887505658916865</v>
       </c>
       <c r="O25">
-        <v>-0.00021823233229966918</v>
+        <v>-0.00021536049324493009</v>
       </c>
       <c r="P25">
-        <v>-0.00019388571336950797</v>
+        <v>-0.00019405216603030507</v>
       </c>
       <c r="Q25">
-        <v>0.00044002168029325421</v>
+        <v>0.00043272826800487568</v>
       </c>
       <c r="R25">
-        <v>0.00018135024026671694</v>
+        <v>0.00012784028704198366</v>
       </c>
       <c r="S25">
-        <v>-6.4812539956370444e-06</v>
+        <v>-2.7170147437050388e-05</v>
       </c>
       <c r="T25">
-        <v>-2.417736306926585e-05</v>
+        <v>2.2633020274732615e-05</v>
       </c>
       <c r="U25">
-        <v>3.9544232753743009e-06</v>
+        <v>1.1918264766500042e-05</v>
       </c>
       <c r="V25">
-        <v>0.00013021739258220867</v>
+        <v>0.00012900647662039927</v>
       </c>
       <c r="W25">
-        <v>0.0056003550254638841</v>
+        <v>0.0056096126105041749</v>
       </c>
       <c r="X25">
-        <v>0.005588998046554443</v>
+        <v>0.0055975466463629043</v>
       </c>
       <c r="Y25">
-        <v>0.0055853909579848295</v>
+        <v>0.0055979776750722339</v>
       </c>
       <c r="Z25">
-        <v>0.0064675273863785271</v>
+        <v>0.006469535202487945</v>
       </c>
       <c r="AA25">
-        <v>0.0055910075039708072</v>
+        <v>0.0056007274304517964</v>
       </c>
       <c r="AB25">
-        <v>0.0055793096485652945</v>
+        <v>0.0055867791216551045</v>
       </c>
       <c r="AC25">
-        <v>1.9620955763014466e-06</v>
+        <v>1.4202039484412414e-06</v>
       </c>
       <c r="AD25">
-        <v>2.1325139556028615e-06</v>
+        <v>-1.2177033538397688e-06</v>
       </c>
       <c r="AE25">
-        <v>1.0190866489515104e-05</v>
+        <v>1.2426743780448099e-05</v>
       </c>
       <c r="AF25">
-        <v>-0.0081469642765172531</v>
+        <v>-0.00827618962564141</v>
       </c>
     </row>
     <row r="26">
@@ -4867,97 +4867,97 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>0.20537885973884176</v>
+        <v>0.20219026314534</v>
       </c>
       <c r="C26">
-        <v>0.00012388701297518954</v>
+        <v>0.00010818608546091598</v>
       </c>
       <c r="D26">
-        <v>7.5648819666561395e-05</v>
+        <v>9.9680704468585457e-05</v>
       </c>
       <c r="E26">
-        <v>-4.9821489612415087e-07</v>
+        <v>-6.8591618313773562e-07</v>
       </c>
       <c r="F26">
-        <v>-1.5450365248449727e-05</v>
+        <v>-2.615179518489566e-06</v>
       </c>
       <c r="G26">
-        <v>-0.00015583452042863821</v>
+        <v>-0.00015847080904152558</v>
       </c>
       <c r="H26">
-        <v>9.1864724172606199e-05</v>
+        <v>8.7246765201815511e-05</v>
       </c>
       <c r="I26">
-        <v>-0.00011077226515824007</v>
+        <v>-0.00011108130216969212</v>
       </c>
       <c r="J26">
-        <v>3.6914701583406692e-05</v>
+        <v>3.8227683195932172e-05</v>
       </c>
       <c r="K26">
-        <v>-0.00020067173771618776</v>
+        <v>-0.0001951670658954595</v>
       </c>
       <c r="L26">
-        <v>3.855480742998409e-05</v>
+        <v>2.1387047368748562e-05</v>
       </c>
       <c r="M26">
-        <v>-0.00013977880512156812</v>
+        <v>-0.00013600591306319029</v>
       </c>
       <c r="N26">
-        <v>-0.00028770017743928798</v>
+        <v>-0.00028005638457713684</v>
       </c>
       <c r="O26">
-        <v>-0.00034910654710936461</v>
+        <v>-0.00034239409481394325</v>
       </c>
       <c r="P26">
-        <v>-0.00032793406210695315</v>
+        <v>-0.00032387872231870365</v>
       </c>
       <c r="Q26">
-        <v>0.00022695569696376585</v>
+        <v>0.00022044725784620934</v>
       </c>
       <c r="R26">
-        <v>0.00011683960778865706</v>
+        <v>0.0001192564933582504</v>
       </c>
       <c r="S26">
-        <v>3.2374485291783483e-05</v>
+        <v>-3.1612628740141854e-05</v>
       </c>
       <c r="T26">
-        <v>2.4388886001330216e-05</v>
+        <v>-0.00012648232008996389</v>
       </c>
       <c r="U26">
-        <v>1.2193991519297951e-05</v>
+        <v>2.0337663410299181e-05</v>
       </c>
       <c r="V26">
-        <v>4.1623959418040041e-05</v>
+        <v>4.6779451483714639e-05</v>
       </c>
       <c r="W26">
-        <v>0.0055900887204728437</v>
+        <v>0.0056020299962277319</v>
       </c>
       <c r="X26">
-        <v>0.005594063523029282</v>
+        <v>0.0056063691318284118</v>
       </c>
       <c r="Y26">
-        <v>0.0055865387760219978</v>
+        <v>0.0056023363320036202</v>
       </c>
       <c r="Z26">
-        <v>0.0055910075039708072</v>
+        <v>0.0056007274304517964</v>
       </c>
       <c r="AA26">
-        <v>0.0062775716921203454</v>
+        <v>0.0062919386641834708</v>
       </c>
       <c r="AB26">
-        <v>0.0055641582263380469</v>
+        <v>0.0055752842344851351</v>
       </c>
       <c r="AC26">
-        <v>-1.114601365970909e-06</v>
+        <v>-1.1625259043383916e-06</v>
       </c>
       <c r="AD26">
-        <v>-1.1979624869085364e-05</v>
+        <v>-1.7669484237886222e-05</v>
       </c>
       <c r="AE26">
-        <v>-4.6923454415907393e-05</v>
+        <v>-4.7732134044238582e-05</v>
       </c>
       <c r="AF26">
-        <v>-0.0081163562147327471</v>
+        <v>-0.0088774891191270508</v>
       </c>
     </row>
     <row r="27">
@@ -4965,97 +4965,97 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>0.094328455719131885</v>
+        <v>0.090700948916997357</v>
       </c>
       <c r="C27">
-        <v>2.0847743153764003e-05</v>
+        <v>6.904116465748897e-06</v>
       </c>
       <c r="D27">
-        <v>-2.1534158072024356e-05</v>
+        <v>-7.81267756554474e-06</v>
       </c>
       <c r="E27">
-        <v>1.7642125534409045e-07</v>
+        <v>7.4841568163490618e-08</v>
       </c>
       <c r="F27">
-        <v>2.2784830465763517e-05</v>
+        <v>2.8694224247772376e-05</v>
       </c>
       <c r="G27">
-        <v>-5.9981935310825935e-05</v>
+        <v>-6.1231019737612719e-05</v>
       </c>
       <c r="H27">
-        <v>0.00012677015335271161</v>
+        <v>0.0001216628739850352</v>
       </c>
       <c r="I27">
-        <v>-0.00011622786640813599</v>
+        <v>-0.0001170967151515451</v>
       </c>
       <c r="J27">
-        <v>1.8256000519498855e-05</v>
+        <v>2.333301139561747e-05</v>
       </c>
       <c r="K27">
-        <v>-0.00035836503714540766</v>
+        <v>-0.00035260073014265619</v>
       </c>
       <c r="L27">
-        <v>0.00017665281624254948</v>
+        <v>0.00016773148791221059</v>
       </c>
       <c r="M27">
-        <v>-4.0230297744125077e-05</v>
+        <v>-3.7767557070671242e-05</v>
       </c>
       <c r="N27">
-        <v>-0.00020856127885315033</v>
+        <v>-0.00020339001972587178</v>
       </c>
       <c r="O27">
-        <v>-0.00022080638520407311</v>
+        <v>-0.00021777243440040928</v>
       </c>
       <c r="P27">
-        <v>-0.00015545698381863246</v>
+        <v>-0.00015439345875577432</v>
       </c>
       <c r="Q27">
-        <v>0.0003164770103205837</v>
+        <v>0.00030965431843519556</v>
       </c>
       <c r="R27">
-        <v>0.00015333264016528103</v>
+        <v>0.00013048039836500384</v>
       </c>
       <c r="S27">
-        <v>-2.9013127443377508e-05</v>
+        <v>8.5678058381575238e-05</v>
       </c>
       <c r="T27">
-        <v>0.00011918428849947609</v>
+        <v>-2.6678346156877066e-05</v>
       </c>
       <c r="U27">
-        <v>-1.568933238852414e-05</v>
+        <v>-1.0155547831822251e-05</v>
       </c>
       <c r="V27">
-        <v>6.1840868144289005e-05</v>
+        <v>6.1309649792859797e-05</v>
       </c>
       <c r="W27">
-        <v>0.005565013506240675</v>
+        <v>0.0055751490951724235</v>
       </c>
       <c r="X27">
-        <v>0.0055470854162039032</v>
+        <v>0.0055571625800598769</v>
       </c>
       <c r="Y27">
-        <v>0.0055367004762778343</v>
+        <v>0.0055501722043315629</v>
       </c>
       <c r="Z27">
-        <v>0.0055793096485652945</v>
+        <v>0.0055867791216551045</v>
       </c>
       <c r="AA27">
-        <v>0.0055641582263380469</v>
+        <v>0.0055752842344851351</v>
       </c>
       <c r="AB27">
-        <v>0.0064173170190779073</v>
+        <v>0.0064263435122981277</v>
       </c>
       <c r="AC27">
-        <v>-6.8085806861010984e-07</v>
+        <v>-1.033716147270756e-06</v>
       </c>
       <c r="AD27">
-        <v>-1.0562724558663486e-05</v>
+        <v>-1.1612915465998835e-05</v>
       </c>
       <c r="AE27">
-        <v>-7.4102342771872887e-06</v>
+        <v>-6.1415532766426889e-06</v>
       </c>
       <c r="AF27">
-        <v>-0.0046728760345997357</v>
+        <v>-0.0051189027836808718</v>
       </c>
     </row>
     <row r="28">
@@ -5063,97 +5063,97 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-0.012765603020222923</v>
+        <v>-0.012784743266723547</v>
       </c>
       <c r="C28">
-        <v>3.9004104743595812e-06</v>
+        <v>2.5353164022284618e-06</v>
       </c>
       <c r="D28">
-        <v>7.954545316162789e-06</v>
+        <v>7.9028390590845342e-06</v>
       </c>
       <c r="E28">
-        <v>-8.8276431555639443e-08</v>
+        <v>-8.6962150874775284e-08</v>
       </c>
       <c r="F28">
-        <v>-2.562358652305935e-05</v>
+        <v>-2.65208927625434e-05</v>
       </c>
       <c r="G28">
-        <v>-2.1539599776004468e-05</v>
+        <v>-2.1592680214786318e-05</v>
       </c>
       <c r="H28">
-        <v>-1.2375192441873928e-07</v>
+        <v>-7.5258779324508928e-08</v>
       </c>
       <c r="I28">
-        <v>1.9269307085190652e-05</v>
+        <v>1.9389961749731991e-05</v>
       </c>
       <c r="J28">
-        <v>3.0587791750546361e-05</v>
+        <v>3.1534090340889229e-05</v>
       </c>
       <c r="K28">
-        <v>1.0989811566303209e-05</v>
+        <v>1.0821262241786595e-05</v>
       </c>
       <c r="L28">
-        <v>1.2996587300830454e-05</v>
+        <v>1.338068976918949e-05</v>
       </c>
       <c r="M28">
-        <v>1.0302928446353325e-05</v>
+        <v>1.0084306560428356e-05</v>
       </c>
       <c r="N28">
-        <v>1.4548855961440797e-05</v>
+        <v>1.4648079613180153e-05</v>
       </c>
       <c r="O28">
-        <v>3.0786045339419217e-05</v>
+        <v>3.0603459678323622e-05</v>
       </c>
       <c r="P28">
-        <v>2.900263651559643e-05</v>
+        <v>2.8749809877302813e-05</v>
       </c>
       <c r="Q28">
-        <v>-2.7909371255910195e-06</v>
+        <v>-2.8648510659164898e-06</v>
       </c>
       <c r="R28">
-        <v>4.7143973248359785e-06</v>
+        <v>1.0884319646008893e-08</v>
       </c>
       <c r="S28">
-        <v>3.0286934443505986e-06</v>
+        <v>1.5624033055573806e-05</v>
       </c>
       <c r="T28">
-        <v>1.3435094568229044e-05</v>
+        <v>5.5367129802432136e-06</v>
       </c>
       <c r="U28">
-        <v>1.9161655377142548e-05</v>
+        <v>1.9886218302450158e-05</v>
       </c>
       <c r="V28">
-        <v>1.2279161423655032e-06</v>
+        <v>1.2533754994691592e-06</v>
       </c>
       <c r="W28">
-        <v>2.4294431255898242e-06</v>
+        <v>2.2049455490788755e-06</v>
       </c>
       <c r="X28">
-        <v>3.1124652425375121e-06</v>
+        <v>2.8547976749440013e-06</v>
       </c>
       <c r="Y28">
-        <v>1.0668804859240165e-05</v>
+        <v>1.076773712683325e-05</v>
       </c>
       <c r="Z28">
-        <v>1.9620955763014466e-06</v>
+        <v>1.4202039484412414e-06</v>
       </c>
       <c r="AA28">
-        <v>-1.114601365970909e-06</v>
+        <v>-1.1625259043383916e-06</v>
       </c>
       <c r="AB28">
-        <v>-6.8085806861010984e-07</v>
+        <v>-1.033716147270756e-06</v>
       </c>
       <c r="AC28">
-        <v>1.1327667015425617e-05</v>
+        <v>1.1325146511577549e-05</v>
       </c>
       <c r="AD28">
-        <v>-5.1766632662052309e-05</v>
+        <v>-5.1944754159041914e-05</v>
       </c>
       <c r="AE28">
-        <v>-6.1226596975042628e-05</v>
+        <v>-6.1322572801623265e-05</v>
       </c>
       <c r="AF28">
-        <v>-0.00040434643266515922</v>
+        <v>-0.00040443249410909276</v>
       </c>
     </row>
     <row r="29">
@@ -5161,97 +5161,97 @@
         <v>51</v>
       </c>
       <c r="B29">
-        <v>-0.10174073730846028</v>
+        <v>-0.10375050595729865</v>
       </c>
       <c r="C29">
-        <v>-3.2800634213444929e-05</v>
+        <v>-2.3776572513753403e-05</v>
       </c>
       <c r="D29">
-        <v>-2.3302600625496606e-05</v>
+        <v>-3.6344385382469646e-05</v>
       </c>
       <c r="E29">
-        <v>8.8175852370998235e-08</v>
+        <v>1.9120497312020849e-07</v>
       </c>
       <c r="F29">
-        <v>1.9954943073725862e-05</v>
+        <v>1.2217974530180642e-05</v>
       </c>
       <c r="G29">
-        <v>-5.2777360766777942e-05</v>
+        <v>-5.6279052144281305e-05</v>
       </c>
       <c r="H29">
-        <v>6.6943520880069843e-06</v>
+        <v>5.0381547394161199e-06</v>
       </c>
       <c r="I29">
-        <v>-8.1355723930311825e-06</v>
+        <v>-8.5274694678563897e-06</v>
       </c>
       <c r="J29">
-        <v>0.00012025088819238305</v>
+        <v>0.00012208290770163513</v>
       </c>
       <c r="K29">
-        <v>3.6627567156484659e-05</v>
+        <v>3.6093097805065867e-05</v>
       </c>
       <c r="L29">
-        <v>-4.2586947257999309e-05</v>
+        <v>-4.2790836759010187e-05</v>
       </c>
       <c r="M29">
-        <v>-6.366220707879457e-05</v>
+        <v>-6.3177250266289336e-05</v>
       </c>
       <c r="N29">
-        <v>-1.3244629703063927e-05</v>
+        <v>-1.5044552863043405e-05</v>
       </c>
       <c r="O29">
-        <v>-7.2938601358510553e-05</v>
+        <v>-7.6728373431216371e-05</v>
       </c>
       <c r="P29">
-        <v>-6.7969074724705996e-05</v>
+        <v>-6.9070441358058026e-05</v>
       </c>
       <c r="Q29">
-        <v>-5.8552944791506577e-05</v>
+        <v>-5.9196877903071657e-05</v>
       </c>
       <c r="R29">
-        <v>6.0870600581627811e-05</v>
+        <v>6.0972931589001102e-05</v>
       </c>
       <c r="S29">
-        <v>-0.00011249496239385979</v>
+        <v>-0.00017872411875424592</v>
       </c>
       <c r="T29">
-        <v>-0.00019424870032547529</v>
+        <v>7.5151238037992826e-05</v>
       </c>
       <c r="U29">
-        <v>-2.6469572485578251e-05</v>
+        <v>-3.1775308139086621e-05</v>
       </c>
       <c r="V29">
-        <v>1.4801331372515415e-05</v>
+        <v>1.0683123865898217e-05</v>
       </c>
       <c r="W29">
-        <v>2.1212966939832944e-05</v>
+        <v>1.8804419656084275e-05</v>
       </c>
       <c r="X29">
-        <v>3.9751670041318415e-05</v>
+        <v>3.6772286860930646e-05</v>
       </c>
       <c r="Y29">
-        <v>-6.4647051522359654e-05</v>
+        <v>-6.970219717220439e-05</v>
       </c>
       <c r="Z29">
-        <v>2.1325139556028615e-06</v>
+        <v>-1.2177033538397688e-06</v>
       </c>
       <c r="AA29">
-        <v>-1.1979624869085364e-05</v>
+        <v>-1.7669484237886222e-05</v>
       </c>
       <c r="AB29">
-        <v>-1.0562724558663486e-05</v>
+        <v>-1.1612915465998835e-05</v>
       </c>
       <c r="AC29">
-        <v>-5.1766632662052309e-05</v>
+        <v>-5.1944754159041914e-05</v>
       </c>
       <c r="AD29">
-        <v>0.0020024169521837211</v>
+        <v>0.0019972247089062828</v>
       </c>
       <c r="AE29">
-        <v>0.00051836651356838208</v>
+        <v>0.00052015278159011269</v>
       </c>
       <c r="AF29">
-        <v>0.0018339807106376935</v>
+        <v>0.0022454379278869395</v>
       </c>
     </row>
     <row r="30">
@@ -5259,97 +5259,97 @@
         <v>52</v>
       </c>
       <c r="B30">
-        <v>-0.14254022296654414</v>
+        <v>-0.14415804782230582</v>
       </c>
       <c r="C30">
-        <v>-1.6362622963248278e-05</v>
+        <v>-6.2605724090432444e-06</v>
       </c>
       <c r="D30">
-        <v>-0.00011881164137514388</v>
+        <v>-0.00011806164469294056</v>
       </c>
       <c r="E30">
-        <v>8.6192674716333495e-07</v>
+        <v>8.4897259201063401e-07</v>
       </c>
       <c r="F30">
-        <v>4.1295043706562895e-05</v>
+        <v>4.8669687654673971e-05</v>
       </c>
       <c r="G30">
-        <v>4.4807082904333578e-05</v>
+        <v>4.852695168872101e-05</v>
       </c>
       <c r="H30">
-        <v>-7.5394154640962691e-06</v>
+        <v>-8.4157082835525834e-06</v>
       </c>
       <c r="I30">
-        <v>7.5426767904021802e-06</v>
+        <v>6.5353898931124832e-06</v>
       </c>
       <c r="J30">
-        <v>1.539995397804167e-05</v>
+        <v>8.8173611989782186e-06</v>
       </c>
       <c r="K30">
-        <v>3.6191158535631e-05</v>
+        <v>3.9237592265942796e-05</v>
       </c>
       <c r="L30">
-        <v>-5.668123728520217e-05</v>
+        <v>-6.2428390317280889e-05</v>
       </c>
       <c r="M30">
-        <v>-1.2898703690403159e-05</v>
+        <v>-1.0207168516141178e-05</v>
       </c>
       <c r="N30">
-        <v>1.8165728128279783e-05</v>
+        <v>1.6109562603758331e-05</v>
       </c>
       <c r="O30">
-        <v>-6.0624952156468261e-05</v>
+        <v>-6.0861654323060739e-05</v>
       </c>
       <c r="P30">
-        <v>6.3133461328519595e-06</v>
+        <v>7.8556709443727314e-06</v>
       </c>
       <c r="Q30">
-        <v>-2.0434884494165411e-05</v>
+        <v>-2.0531197943280403e-05</v>
       </c>
       <c r="R30">
-        <v>4.8794614115166062e-05</v>
+        <v>8.481826988177444e-05</v>
       </c>
       <c r="S30">
-        <v>-8.3169900872820044e-05</v>
+        <v>-0.00016821745419701769</v>
       </c>
       <c r="T30">
-        <v>-0.00015139558668159948</v>
+        <v>-5.1538663644032368e-05</v>
       </c>
       <c r="U30">
-        <v>1.1721360213440366e-05</v>
+        <v>6.0271614670592616e-06</v>
       </c>
       <c r="V30">
-        <v>-8.643213029227865e-05</v>
+        <v>-8.60921585123263e-05</v>
       </c>
       <c r="W30">
-        <v>4.3754300290579744e-05</v>
+        <v>4.5988420942344845e-05</v>
       </c>
       <c r="X30">
-        <v>1.4410669271689358e-05</v>
+        <v>1.5565115333169384e-05</v>
       </c>
       <c r="Y30">
-        <v>-3.9905022356864859e-05</v>
+        <v>-4.0481782723951606e-05</v>
       </c>
       <c r="Z30">
-        <v>1.0190866489515104e-05</v>
+        <v>1.2426743780448099e-05</v>
       </c>
       <c r="AA30">
-        <v>-4.6923454415907393e-05</v>
+        <v>-4.7732134044238582e-05</v>
       </c>
       <c r="AB30">
-        <v>-7.4102342771872887e-06</v>
+        <v>-6.1415532766426889e-06</v>
       </c>
       <c r="AC30">
-        <v>-6.1226596975042628e-05</v>
+        <v>-6.1322572801623265e-05</v>
       </c>
       <c r="AD30">
-        <v>0.00051836651356838208</v>
+        <v>0.00052015278159011269</v>
       </c>
       <c r="AE30">
-        <v>0.0018927486686804004</v>
+        <v>0.0018985645626088787</v>
       </c>
       <c r="AF30">
-        <v>0.0048829812015429063</v>
+        <v>0.0048771004306105443</v>
       </c>
     </row>
     <row r="31">
@@ -5357,97 +5357,97 @@
         <v>38</v>
       </c>
       <c r="B31">
-        <v>-3.8266336296705879</v>
+        <v>-3.4766705973745746</v>
       </c>
       <c r="C31">
-        <v>-0.0098211081736195426</v>
+        <v>-0.010362830863151266</v>
       </c>
       <c r="D31">
-        <v>-0.12073367643394517</v>
+        <v>-0.12185803817751206</v>
       </c>
       <c r="E31">
-        <v>0.00098004909252421158</v>
+        <v>0.0009899097002269196</v>
       </c>
       <c r="F31">
-        <v>0.090213049877748031</v>
+        <v>0.08891250148184171</v>
       </c>
       <c r="G31">
-        <v>0.083696769059056486</v>
+        <v>0.082591000956276639</v>
       </c>
       <c r="H31">
-        <v>-0.00088888510185315337</v>
+        <v>-0.00074842086026358917</v>
       </c>
       <c r="I31">
-        <v>0.00011886449373839716</v>
+        <v>0.00024179104459880023</v>
       </c>
       <c r="J31">
-        <v>-0.0826777603667746</v>
+        <v>-0.080972410481051138</v>
       </c>
       <c r="K31">
-        <v>0.0017422100399287297</v>
+        <v>0.0015604631246996618</v>
       </c>
       <c r="L31">
-        <v>-0.020037704559520836</v>
+        <v>-0.019576070744094704</v>
       </c>
       <c r="M31">
-        <v>-0.0039375238607508162</v>
+        <v>-0.0036488735544846183</v>
       </c>
       <c r="N31">
-        <v>0.0022686468873432813</v>
+        <v>0.0022789462033859474</v>
       </c>
       <c r="O31">
-        <v>-0.00061661017433234378</v>
+        <v>-0.00082375056725186857</v>
       </c>
       <c r="P31">
-        <v>0.0018750322611581632</v>
+        <v>0.0018947356936218698</v>
       </c>
       <c r="Q31">
-        <v>0.0060889401524989763</v>
+        <v>0.006096500656888419</v>
       </c>
       <c r="R31">
-        <v>-0.0043589147659581773</v>
+        <v>-0.0099367354861983545</v>
       </c>
       <c r="S31">
-        <v>0.0083108403005202891</v>
+        <v>0.0070811416908349023</v>
       </c>
       <c r="T31">
-        <v>0.0022384526513898467</v>
+        <v>0.014227122448520785</v>
       </c>
       <c r="U31">
-        <v>0.00092174241503439544</v>
+        <v>0.0010161438826846517</v>
       </c>
       <c r="V31">
-        <v>0.0013660439129549486</v>
+        <v>0.00085672300024444877</v>
       </c>
       <c r="W31">
-        <v>-0.0038754806573304476</v>
+        <v>-0.0042507347105164121</v>
       </c>
       <c r="X31">
-        <v>-0.0064913397276946706</v>
+        <v>-0.0069392962608397398</v>
       </c>
       <c r="Y31">
-        <v>-0.0048444440937379825</v>
+        <v>-0.0057599498240735805</v>
       </c>
       <c r="Z31">
-        <v>-0.0081469642765172531</v>
+        <v>-0.00827618962564141</v>
       </c>
       <c r="AA31">
-        <v>-0.0081163562147327471</v>
+        <v>-0.0088774891191270508</v>
       </c>
       <c r="AB31">
-        <v>-0.0046728760345997357</v>
+        <v>-0.0051189027836808718</v>
       </c>
       <c r="AC31">
-        <v>-0.00040434643266515922</v>
+        <v>-0.00040443249410909276</v>
       </c>
       <c r="AD31">
-        <v>0.0018339807106376935</v>
+        <v>0.0022454379278869395</v>
       </c>
       <c r="AE31">
-        <v>0.0048829812015429063</v>
+        <v>0.0048771004306105443</v>
       </c>
       <c r="AF31">
-        <v>3.7246269383248922</v>
+        <v>3.757441185828533</v>
       </c>
     </row>
   </sheetData>
